--- a/data/parametrosMesuales.xlsx
+++ b/data/parametrosMesuales.xlsx
@@ -1,23 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\proyecto_Ia\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\proyecto_Ia\Version20\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CA577DBB-8C68-4CB8-AB3A-E97E4F62DDE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CE85E75-D8F8-4738-9283-9568A3D012BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-4155" yWindow="-1980" windowWidth="29040" windowHeight="15720" xr2:uid="{4C61D130-B55A-40EB-8581-4AF412B8D4BF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{4C61D130-B55A-40EB-8581-4AF412B8D4BF}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja2" sheetId="2" r:id="rId1"/>
-    <sheet name="Hoja1" sheetId="4" r:id="rId2"/>
+    <sheet name="Hoja1" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="160">
   <si>
     <t>Formato Fecha</t>
   </si>
@@ -433,35 +431,102 @@
     <t>monto_Utm</t>
   </si>
   <si>
-    <t>parametrosMesuales.xlsx — Excel original parámetros mensuales</t>
-  </si>
-  <si>
-    <t>inst_afp.xlsx — instituciones AFP</t>
-  </si>
-  <si>
-    <t>afp_previred.xlsx — códigos Previred de referencia</t>
-  </si>
-  <si>
-    <t>inst_apv.xlsx — instituciones APV</t>
-  </si>
-  <si>
-    <t>inst_cajas.xlsx — cajas de compensación</t>
-  </si>
-  <si>
-    <t>inst_mutuales.xlsx — mutualidades</t>
-  </si>
-  <si>
-    <t>inst_salud.xlsx — instituciones de salud</t>
+    <t>2026-05</t>
+  </si>
+  <si>
+    <t>2026-06</t>
+  </si>
+  <si>
+    <t>2026-07</t>
+  </si>
+  <si>
+    <t>2026-08</t>
+  </si>
+  <si>
+    <t>2026-09</t>
+  </si>
+  <si>
+    <t>2026-10</t>
+  </si>
+  <si>
+    <t>2026-11</t>
+  </si>
+  <si>
+    <t>2026-12</t>
+  </si>
+  <si>
+    <t>2027-01</t>
+  </si>
+  <si>
+    <t>2027-02</t>
+  </si>
+  <si>
+    <t>2027-03</t>
+  </si>
+  <si>
+    <t>2027-04</t>
+  </si>
+  <si>
+    <t>2027-05</t>
+  </si>
+  <si>
+    <t>2027-06</t>
+  </si>
+  <si>
+    <t>2027-07</t>
+  </si>
+  <si>
+    <t>2027-08</t>
+  </si>
+  <si>
+    <t>2027-09</t>
+  </si>
+  <si>
+    <t>2027-10</t>
+  </si>
+  <si>
+    <t>2027-11</t>
+  </si>
+  <si>
+    <t>2027-12</t>
+  </si>
+  <si>
+    <t>aporteFAPPBAC</t>
+  </si>
+  <si>
+    <t>ExpVida_Sis</t>
+  </si>
+  <si>
+    <t>2028-01</t>
+  </si>
+  <si>
+    <t>2028-02</t>
+  </si>
+  <si>
+    <t>2028-03</t>
+  </si>
+  <si>
+    <t>2028-04</t>
+  </si>
+  <si>
+    <t>2028-05</t>
+  </si>
+  <si>
+    <t>2028-06</t>
+  </si>
+  <si>
+    <t>2028-07</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="164" formatCode="dd/mm/aaaa"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -480,6 +545,12 @@
       <b/>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -505,7 +576,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -528,12 +599,36 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -542,6 +637,17 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Millares [0]" xfId="1" builtinId="6"/>
@@ -877,7 +983,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A8E14BD-A912-4688-A47A-8948A43ADEEA}">
-  <dimension ref="A1:S113"/>
+  <dimension ref="A1:U140"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -899,9 +1005,11 @@
     <col min="17" max="17" width="15" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="11.28515625" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>115</v>
       </c>
@@ -950,17 +1058,23 @@
       <c r="P1" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="Q1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="R1" s="5" t="s">
+      <c r="Q1" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="R1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="S1" s="15" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T1" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="U1" s="12" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1010,15 +1124,25 @@
         <v>31</v>
       </c>
       <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
-      <c r="Q2" s="4" t="str">
-        <f>_xlfn.CONCAT(N2,"/","01/2017")</f>
-        <v>31/01/2017</v>
-      </c>
-      <c r="R2" s="2"/>
-      <c r="S2" s="4"/>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="P2" s="1"/>
+      <c r="Q2" s="10" t="str">
+        <f>_xlfn.CONCAT(N2,"-",RIGHT(A2,2),"-",LEFT(A2,4))</f>
+        <v>31-01-2017</v>
+      </c>
+      <c r="R2" s="2">
+        <v>0</v>
+      </c>
+      <c r="S2" s="2">
+        <v>0</v>
+      </c>
+      <c r="T2" s="2">
+        <v>0</v>
+      </c>
+      <c r="U2" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1068,15 +1192,25 @@
         <v>28</v>
       </c>
       <c r="O3" s="2"/>
-      <c r="P3" s="2"/>
-      <c r="Q3" s="4" t="str">
-        <f>_xlfn.CONCAT(N3,"/","02/2017")</f>
-        <v>28/02/2017</v>
-      </c>
-      <c r="R3" s="4"/>
-      <c r="S3" s="4"/>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="P3" s="1"/>
+      <c r="Q3" s="10" t="str">
+        <f t="shared" ref="Q3:Q66" si="6">_xlfn.CONCAT(N3,"-",RIGHT(A3,2),"-",LEFT(A3,4))</f>
+        <v>28-02-2017</v>
+      </c>
+      <c r="R3" s="2">
+        <v>0</v>
+      </c>
+      <c r="S3" s="2">
+        <v>0</v>
+      </c>
+      <c r="T3" s="2">
+        <v>0</v>
+      </c>
+      <c r="U3" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -1126,15 +1260,25 @@
         <v>31</v>
       </c>
       <c r="O4" s="2"/>
-      <c r="P4" s="2"/>
-      <c r="Q4" s="4" t="str">
-        <f>_xlfn.CONCAT(N4,"/","03/2017")</f>
-        <v>31/03/2017</v>
-      </c>
-      <c r="R4" s="4"/>
-      <c r="S4" s="4"/>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="P4" s="1"/>
+      <c r="Q4" s="10" t="str">
+        <f t="shared" si="6"/>
+        <v>31-03-2017</v>
+      </c>
+      <c r="R4" s="2">
+        <v>0</v>
+      </c>
+      <c r="S4" s="2">
+        <v>0</v>
+      </c>
+      <c r="T4" s="2">
+        <v>0</v>
+      </c>
+      <c r="U4" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
@@ -1184,15 +1328,25 @@
         <v>30</v>
       </c>
       <c r="O5" s="2"/>
-      <c r="P5" s="2"/>
-      <c r="Q5" s="4" t="str">
-        <f>_xlfn.CONCAT(N5,"/","04/2017")</f>
-        <v>30/04/2017</v>
-      </c>
-      <c r="R5" s="4"/>
-      <c r="S5" s="4"/>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="P5" s="1"/>
+      <c r="Q5" s="10" t="str">
+        <f t="shared" si="6"/>
+        <v>30-04-2017</v>
+      </c>
+      <c r="R5" s="2">
+        <v>0</v>
+      </c>
+      <c r="S5" s="2">
+        <v>0</v>
+      </c>
+      <c r="T5" s="2">
+        <v>0</v>
+      </c>
+      <c r="U5" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
@@ -1242,15 +1396,25 @@
         <v>31</v>
       </c>
       <c r="O6" s="2"/>
-      <c r="P6" s="2"/>
-      <c r="Q6" s="4" t="str">
-        <f>_xlfn.CONCAT(N6,"/","05/2017")</f>
-        <v>31/05/2017</v>
-      </c>
-      <c r="R6" s="4"/>
-      <c r="S6" s="4"/>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="P6" s="1"/>
+      <c r="Q6" s="10" t="str">
+        <f t="shared" si="6"/>
+        <v>31-05-2017</v>
+      </c>
+      <c r="R6" s="2">
+        <v>0</v>
+      </c>
+      <c r="S6" s="2">
+        <v>0</v>
+      </c>
+      <c r="T6" s="2">
+        <v>0</v>
+      </c>
+      <c r="U6" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
@@ -1300,15 +1464,25 @@
         <v>30</v>
       </c>
       <c r="O7" s="2"/>
-      <c r="P7" s="2"/>
-      <c r="Q7" s="4" t="str">
-        <f>_xlfn.CONCAT(N7,"/","06/2017")</f>
-        <v>30/06/2017</v>
-      </c>
-      <c r="R7" s="4"/>
-      <c r="S7" s="4"/>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="P7" s="1"/>
+      <c r="Q7" s="10" t="str">
+        <f t="shared" si="6"/>
+        <v>30-06-2017</v>
+      </c>
+      <c r="R7" s="2">
+        <v>0</v>
+      </c>
+      <c r="S7" s="2">
+        <v>0</v>
+      </c>
+      <c r="T7" s="2">
+        <v>0</v>
+      </c>
+      <c r="U7" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
@@ -1358,15 +1532,25 @@
         <v>31</v>
       </c>
       <c r="O8" s="2"/>
-      <c r="P8" s="2"/>
-      <c r="Q8" s="4" t="str">
-        <f>_xlfn.CONCAT(N8,"/","07/2017")</f>
-        <v>31/07/2017</v>
-      </c>
-      <c r="R8" s="4"/>
-      <c r="S8" s="4"/>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="P8" s="1"/>
+      <c r="Q8" s="10" t="str">
+        <f t="shared" si="6"/>
+        <v>31-07-2017</v>
+      </c>
+      <c r="R8" s="2">
+        <v>0</v>
+      </c>
+      <c r="S8" s="2">
+        <v>0</v>
+      </c>
+      <c r="T8" s="2">
+        <v>0</v>
+      </c>
+      <c r="U8" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
@@ -1416,15 +1600,25 @@
         <v>31</v>
       </c>
       <c r="O9" s="2"/>
-      <c r="P9" s="2"/>
-      <c r="Q9" s="4" t="str">
-        <f>_xlfn.CONCAT(N9,"/","08/2017")</f>
-        <v>31/08/2017</v>
-      </c>
-      <c r="R9" s="4"/>
-      <c r="S9" s="4"/>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="P9" s="1"/>
+      <c r="Q9" s="10" t="str">
+        <f t="shared" si="6"/>
+        <v>31-08-2017</v>
+      </c>
+      <c r="R9" s="2">
+        <v>0</v>
+      </c>
+      <c r="S9" s="2">
+        <v>0</v>
+      </c>
+      <c r="T9" s="2">
+        <v>0</v>
+      </c>
+      <c r="U9" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
@@ -1474,15 +1668,25 @@
         <v>30</v>
       </c>
       <c r="O10" s="2"/>
-      <c r="P10" s="2"/>
-      <c r="Q10" s="4" t="str">
-        <f>_xlfn.CONCAT(N10,"/","09/2017")</f>
-        <v>30/09/2017</v>
-      </c>
-      <c r="R10" s="4"/>
-      <c r="S10" s="4"/>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="P10" s="1"/>
+      <c r="Q10" s="10" t="str">
+        <f t="shared" si="6"/>
+        <v>30-09-2017</v>
+      </c>
+      <c r="R10" s="2">
+        <v>0</v>
+      </c>
+      <c r="S10" s="2">
+        <v>0</v>
+      </c>
+      <c r="T10" s="2">
+        <v>0</v>
+      </c>
+      <c r="U10" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>12</v>
       </c>
@@ -1532,15 +1736,25 @@
         <v>31</v>
       </c>
       <c r="O11" s="2"/>
-      <c r="P11" s="2"/>
-      <c r="Q11" s="4" t="str">
-        <f>_xlfn.CONCAT(N11,"/","10/2017")</f>
-        <v>31/10/2017</v>
-      </c>
-      <c r="R11" s="4"/>
-      <c r="S11" s="4"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="P11" s="1"/>
+      <c r="Q11" s="10" t="str">
+        <f t="shared" si="6"/>
+        <v>31-10-2017</v>
+      </c>
+      <c r="R11" s="2">
+        <v>0</v>
+      </c>
+      <c r="S11" s="2">
+        <v>0</v>
+      </c>
+      <c r="T11" s="2">
+        <v>0</v>
+      </c>
+      <c r="U11" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>13</v>
       </c>
@@ -1590,15 +1804,25 @@
         <v>30</v>
       </c>
       <c r="O12" s="2"/>
-      <c r="P12" s="2"/>
-      <c r="Q12" s="4" t="str">
-        <f>_xlfn.CONCAT(N12,"/","11/2017")</f>
-        <v>30/11/2017</v>
-      </c>
-      <c r="R12" s="4"/>
-      <c r="S12" s="4"/>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="P12" s="1"/>
+      <c r="Q12" s="10" t="str">
+        <f t="shared" si="6"/>
+        <v>30-11-2017</v>
+      </c>
+      <c r="R12" s="2">
+        <v>0</v>
+      </c>
+      <c r="S12" s="2">
+        <v>0</v>
+      </c>
+      <c r="T12" s="2">
+        <v>0</v>
+      </c>
+      <c r="U12" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>14</v>
       </c>
@@ -1648,15 +1872,25 @@
         <v>31</v>
       </c>
       <c r="O13" s="2"/>
-      <c r="P13" s="2"/>
-      <c r="Q13" s="4" t="str">
-        <f>_xlfn.CONCAT(N13,"/","12/2017")</f>
-        <v>31/12/2017</v>
-      </c>
-      <c r="R13" s="4"/>
-      <c r="S13" s="4"/>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="P13" s="1"/>
+      <c r="Q13" s="10" t="str">
+        <f t="shared" si="6"/>
+        <v>31-12-2017</v>
+      </c>
+      <c r="R13" s="2">
+        <v>0</v>
+      </c>
+      <c r="S13" s="2">
+        <v>0</v>
+      </c>
+      <c r="T13" s="2">
+        <v>0</v>
+      </c>
+      <c r="U13" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>15</v>
       </c>
@@ -1706,15 +1940,25 @@
         <v>31</v>
       </c>
       <c r="O14" s="2"/>
-      <c r="P14" s="2"/>
-      <c r="Q14" s="4" t="str">
-        <f>_xlfn.CONCAT(N14,"/","01/2018")</f>
-        <v>31/01/2018</v>
-      </c>
-      <c r="R14" s="4"/>
-      <c r="S14" s="4"/>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="P14" s="1"/>
+      <c r="Q14" s="10" t="str">
+        <f t="shared" si="6"/>
+        <v>31-01-2018</v>
+      </c>
+      <c r="R14" s="2">
+        <v>0</v>
+      </c>
+      <c r="S14" s="2">
+        <v>0</v>
+      </c>
+      <c r="T14" s="2">
+        <v>0</v>
+      </c>
+      <c r="U14" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>16</v>
       </c>
@@ -1764,15 +2008,25 @@
         <v>28</v>
       </c>
       <c r="O15" s="2"/>
-      <c r="P15" s="2"/>
-      <c r="Q15" s="4" t="str">
-        <f>_xlfn.CONCAT(N15,"/","02/2018")</f>
-        <v>28/02/2018</v>
-      </c>
-      <c r="R15" s="4"/>
-      <c r="S15" s="4"/>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="P15" s="1"/>
+      <c r="Q15" s="10" t="str">
+        <f t="shared" si="6"/>
+        <v>28-02-2018</v>
+      </c>
+      <c r="R15" s="2">
+        <v>0</v>
+      </c>
+      <c r="S15" s="2">
+        <v>0</v>
+      </c>
+      <c r="T15" s="2">
+        <v>0</v>
+      </c>
+      <c r="U15" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>17</v>
       </c>
@@ -1822,15 +2076,25 @@
         <v>31</v>
       </c>
       <c r="O16" s="2"/>
-      <c r="P16" s="2"/>
-      <c r="Q16" s="4" t="str">
-        <f>_xlfn.CONCAT(N16,"/","03/2018")</f>
-        <v>31/03/2018</v>
-      </c>
-      <c r="R16" s="4"/>
-      <c r="S16" s="4"/>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="P16" s="1"/>
+      <c r="Q16" s="10" t="str">
+        <f t="shared" si="6"/>
+        <v>31-03-2018</v>
+      </c>
+      <c r="R16" s="2">
+        <v>0</v>
+      </c>
+      <c r="S16" s="2">
+        <v>0</v>
+      </c>
+      <c r="T16" s="2">
+        <v>0</v>
+      </c>
+      <c r="U16" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>18</v>
       </c>
@@ -1880,15 +2144,25 @@
         <v>30</v>
       </c>
       <c r="O17" s="2"/>
-      <c r="P17" s="2"/>
-      <c r="Q17" s="4" t="str">
-        <f>_xlfn.CONCAT(N17,"/","04/2018")</f>
-        <v>30/04/2018</v>
-      </c>
-      <c r="R17" s="4"/>
-      <c r="S17" s="4"/>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="P17" s="1"/>
+      <c r="Q17" s="10" t="str">
+        <f t="shared" si="6"/>
+        <v>30-04-2018</v>
+      </c>
+      <c r="R17" s="2">
+        <v>0</v>
+      </c>
+      <c r="S17" s="2">
+        <v>0</v>
+      </c>
+      <c r="T17" s="2">
+        <v>0</v>
+      </c>
+      <c r="U17" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>19</v>
       </c>
@@ -1938,15 +2212,25 @@
         <v>31</v>
       </c>
       <c r="O18" s="2"/>
-      <c r="P18" s="2"/>
-      <c r="Q18" s="4" t="str">
-        <f>_xlfn.CONCAT(N18,"/","05/2018")</f>
-        <v>31/05/2018</v>
-      </c>
-      <c r="R18" s="4"/>
-      <c r="S18" s="4"/>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="P18" s="1"/>
+      <c r="Q18" s="10" t="str">
+        <f t="shared" si="6"/>
+        <v>31-05-2018</v>
+      </c>
+      <c r="R18" s="2">
+        <v>0</v>
+      </c>
+      <c r="S18" s="2">
+        <v>0</v>
+      </c>
+      <c r="T18" s="2">
+        <v>0</v>
+      </c>
+      <c r="U18" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>20</v>
       </c>
@@ -1996,15 +2280,25 @@
         <v>30</v>
       </c>
       <c r="O19" s="2"/>
-      <c r="P19" s="2"/>
-      <c r="Q19" s="4" t="str">
-        <f>_xlfn.CONCAT(N19,"/","06/2018")</f>
-        <v>30/06/2018</v>
-      </c>
-      <c r="R19" s="4"/>
-      <c r="S19" s="4"/>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="P19" s="1"/>
+      <c r="Q19" s="10" t="str">
+        <f t="shared" si="6"/>
+        <v>30-06-2018</v>
+      </c>
+      <c r="R19" s="2">
+        <v>0</v>
+      </c>
+      <c r="S19" s="2">
+        <v>0</v>
+      </c>
+      <c r="T19" s="2">
+        <v>0</v>
+      </c>
+      <c r="U19" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>21</v>
       </c>
@@ -2054,15 +2348,25 @@
         <v>31</v>
       </c>
       <c r="O20" s="2"/>
-      <c r="P20" s="2"/>
-      <c r="Q20" s="4" t="str">
-        <f>_xlfn.CONCAT(N20,"/","07/2018")</f>
-        <v>31/07/2018</v>
-      </c>
-      <c r="R20" s="4"/>
-      <c r="S20" s="4"/>
-    </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="P20" s="1"/>
+      <c r="Q20" s="10" t="str">
+        <f t="shared" si="6"/>
+        <v>31-07-2018</v>
+      </c>
+      <c r="R20" s="2">
+        <v>0</v>
+      </c>
+      <c r="S20" s="2">
+        <v>0</v>
+      </c>
+      <c r="T20" s="2">
+        <v>0</v>
+      </c>
+      <c r="U20" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>22</v>
       </c>
@@ -2112,15 +2416,25 @@
         <v>31</v>
       </c>
       <c r="O21" s="2"/>
-      <c r="P21" s="2"/>
-      <c r="Q21" s="4" t="str">
-        <f>_xlfn.CONCAT(N21,"/","08/2018")</f>
-        <v>31/08/2018</v>
-      </c>
-      <c r="R21" s="4"/>
-      <c r="S21" s="4"/>
-    </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="P21" s="1"/>
+      <c r="Q21" s="10" t="str">
+        <f t="shared" si="6"/>
+        <v>31-08-2018</v>
+      </c>
+      <c r="R21" s="2">
+        <v>0</v>
+      </c>
+      <c r="S21" s="2">
+        <v>0</v>
+      </c>
+      <c r="T21" s="2">
+        <v>0</v>
+      </c>
+      <c r="U21" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>23</v>
       </c>
@@ -2170,15 +2484,25 @@
         <v>30</v>
       </c>
       <c r="O22" s="2"/>
-      <c r="P22" s="2"/>
-      <c r="Q22" s="4" t="str">
-        <f>_xlfn.CONCAT(N22,"/","09/2018")</f>
-        <v>30/09/2018</v>
-      </c>
-      <c r="R22" s="4"/>
-      <c r="S22" s="4"/>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="P22" s="1"/>
+      <c r="Q22" s="10" t="str">
+        <f t="shared" si="6"/>
+        <v>30-09-2018</v>
+      </c>
+      <c r="R22" s="2">
+        <v>0</v>
+      </c>
+      <c r="S22" s="2">
+        <v>0</v>
+      </c>
+      <c r="T22" s="2">
+        <v>0</v>
+      </c>
+      <c r="U22" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>24</v>
       </c>
@@ -2228,15 +2552,25 @@
         <v>31</v>
       </c>
       <c r="O23" s="2"/>
-      <c r="P23" s="2"/>
-      <c r="Q23" s="4" t="str">
-        <f>_xlfn.CONCAT(N23,"/","10/2018")</f>
-        <v>31/10/2018</v>
-      </c>
-      <c r="R23" s="4"/>
-      <c r="S23" s="4"/>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="P23" s="1"/>
+      <c r="Q23" s="10" t="str">
+        <f t="shared" si="6"/>
+        <v>31-10-2018</v>
+      </c>
+      <c r="R23" s="2">
+        <v>0</v>
+      </c>
+      <c r="S23" s="2">
+        <v>0</v>
+      </c>
+      <c r="T23" s="2">
+        <v>0</v>
+      </c>
+      <c r="U23" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>25</v>
       </c>
@@ -2286,15 +2620,25 @@
         <v>30</v>
       </c>
       <c r="O24" s="2"/>
-      <c r="P24" s="2"/>
-      <c r="Q24" s="4" t="str">
-        <f>_xlfn.CONCAT(N24,"/","11/2018")</f>
-        <v>30/11/2018</v>
-      </c>
-      <c r="R24" s="4"/>
-      <c r="S24" s="4"/>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="P24" s="1"/>
+      <c r="Q24" s="10" t="str">
+        <f t="shared" si="6"/>
+        <v>30-11-2018</v>
+      </c>
+      <c r="R24" s="2">
+        <v>0</v>
+      </c>
+      <c r="S24" s="2">
+        <v>0</v>
+      </c>
+      <c r="T24" s="2">
+        <v>0</v>
+      </c>
+      <c r="U24" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>26</v>
       </c>
@@ -2344,15 +2688,25 @@
         <v>31</v>
       </c>
       <c r="O25" s="2"/>
-      <c r="P25" s="2"/>
-      <c r="Q25" s="4" t="str">
-        <f>_xlfn.CONCAT(N25,"/","12/2018")</f>
-        <v>31/12/2018</v>
-      </c>
-      <c r="R25" s="4"/>
-      <c r="S25" s="4"/>
-    </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="P25" s="1"/>
+      <c r="Q25" s="10" t="str">
+        <f t="shared" si="6"/>
+        <v>31-12-2018</v>
+      </c>
+      <c r="R25" s="2">
+        <v>0</v>
+      </c>
+      <c r="S25" s="2">
+        <v>0</v>
+      </c>
+      <c r="T25" s="2">
+        <v>0</v>
+      </c>
+      <c r="U25" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>27</v>
       </c>
@@ -2402,18 +2756,28 @@
         <v>31</v>
       </c>
       <c r="O26" s="2"/>
-      <c r="P26" s="2">
+      <c r="P26" s="1">
         <f>7-O26</f>
         <v>7</v>
       </c>
-      <c r="Q26" s="4" t="str">
-        <f>_xlfn.CONCAT(N26,"/","01/2019")</f>
-        <v>31/01/2019</v>
-      </c>
-      <c r="R26" s="4"/>
-      <c r="S26" s="4"/>
-    </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q26" s="10" t="str">
+        <f t="shared" si="6"/>
+        <v>31-01-2019</v>
+      </c>
+      <c r="R26" s="2">
+        <v>0</v>
+      </c>
+      <c r="S26" s="2">
+        <v>0</v>
+      </c>
+      <c r="T26" s="2">
+        <v>0</v>
+      </c>
+      <c r="U26" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>28</v>
       </c>
@@ -2463,18 +2827,28 @@
         <v>28</v>
       </c>
       <c r="O27" s="2"/>
-      <c r="P27" s="2">
-        <f t="shared" ref="P27:P67" si="6">7-O27</f>
+      <c r="P27" s="1">
+        <f t="shared" ref="P27:P67" si="7">7-O27</f>
         <v>7</v>
       </c>
-      <c r="Q27" s="4" t="str">
-        <f>_xlfn.CONCAT(N27,"/","02/2019")</f>
-        <v>28/02/2019</v>
-      </c>
-      <c r="R27" s="4"/>
-      <c r="S27" s="4"/>
-    </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q27" s="10" t="str">
+        <f t="shared" si="6"/>
+        <v>28-02-2019</v>
+      </c>
+      <c r="R27" s="2">
+        <v>0</v>
+      </c>
+      <c r="S27" s="2">
+        <v>0</v>
+      </c>
+      <c r="T27" s="2">
+        <v>0</v>
+      </c>
+      <c r="U27" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>29</v>
       </c>
@@ -2524,18 +2898,28 @@
         <v>31</v>
       </c>
       <c r="O28" s="2"/>
-      <c r="P28" s="2">
+      <c r="P28" s="1">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="Q28" s="10" t="str">
         <f t="shared" si="6"/>
-        <v>7</v>
-      </c>
-      <c r="Q28" s="4" t="str">
-        <f>_xlfn.CONCAT(N28,"/","03/2019")</f>
-        <v>31/03/2019</v>
-      </c>
-      <c r="R28" s="4"/>
-      <c r="S28" s="4"/>
-    </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+        <v>31-03-2019</v>
+      </c>
+      <c r="R28" s="2">
+        <v>0</v>
+      </c>
+      <c r="S28" s="2">
+        <v>0</v>
+      </c>
+      <c r="T28" s="2">
+        <v>0</v>
+      </c>
+      <c r="U28" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>30</v>
       </c>
@@ -2585,18 +2969,28 @@
         <v>30</v>
       </c>
       <c r="O29" s="2"/>
-      <c r="P29" s="2">
+      <c r="P29" s="1">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="Q29" s="10" t="str">
         <f t="shared" si="6"/>
-        <v>7</v>
-      </c>
-      <c r="Q29" s="4" t="str">
-        <f>_xlfn.CONCAT(N29,"/","04/2019")</f>
-        <v>30/04/2019</v>
-      </c>
-      <c r="R29" s="4"/>
-      <c r="S29" s="4"/>
-    </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+        <v>30-04-2019</v>
+      </c>
+      <c r="R29" s="2">
+        <v>0</v>
+      </c>
+      <c r="S29" s="2">
+        <v>0</v>
+      </c>
+      <c r="T29" s="2">
+        <v>0</v>
+      </c>
+      <c r="U29" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>31</v>
       </c>
@@ -2646,18 +3040,28 @@
         <v>31</v>
       </c>
       <c r="O30" s="2"/>
-      <c r="P30" s="2">
+      <c r="P30" s="1">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="Q30" s="10" t="str">
         <f t="shared" si="6"/>
-        <v>7</v>
-      </c>
-      <c r="Q30" s="4" t="str">
-        <f>_xlfn.CONCAT(N30,"/","05/2019")</f>
-        <v>31/05/2019</v>
-      </c>
-      <c r="R30" s="4"/>
-      <c r="S30" s="4"/>
-    </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+        <v>31-05-2019</v>
+      </c>
+      <c r="R30" s="2">
+        <v>0</v>
+      </c>
+      <c r="S30" s="2">
+        <v>0</v>
+      </c>
+      <c r="T30" s="2">
+        <v>0</v>
+      </c>
+      <c r="U30" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>32</v>
       </c>
@@ -2707,18 +3111,28 @@
         <v>30</v>
       </c>
       <c r="O31" s="2"/>
-      <c r="P31" s="2">
+      <c r="P31" s="1">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="Q31" s="10" t="str">
         <f t="shared" si="6"/>
-        <v>7</v>
-      </c>
-      <c r="Q31" s="4" t="str">
-        <f>_xlfn.CONCAT(N31,"/","06/2019")</f>
-        <v>30/06/2019</v>
-      </c>
-      <c r="R31" s="4"/>
-      <c r="S31" s="4"/>
-    </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+        <v>30-06-2019</v>
+      </c>
+      <c r="R31" s="2">
+        <v>0</v>
+      </c>
+      <c r="S31" s="2">
+        <v>0</v>
+      </c>
+      <c r="T31" s="2">
+        <v>0</v>
+      </c>
+      <c r="U31" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>33</v>
       </c>
@@ -2768,18 +3182,28 @@
         <v>31</v>
       </c>
       <c r="O32" s="2"/>
-      <c r="P32" s="2">
+      <c r="P32" s="1">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="Q32" s="10" t="str">
         <f t="shared" si="6"/>
-        <v>7</v>
-      </c>
-      <c r="Q32" s="4" t="str">
-        <f>_xlfn.CONCAT(N32,"/","07/2019")</f>
-        <v>31/07/2019</v>
-      </c>
-      <c r="R32" s="4"/>
-      <c r="S32" s="4"/>
-    </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+        <v>31-07-2019</v>
+      </c>
+      <c r="R32" s="2">
+        <v>0</v>
+      </c>
+      <c r="S32" s="2">
+        <v>0</v>
+      </c>
+      <c r="T32" s="2">
+        <v>0</v>
+      </c>
+      <c r="U32" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>34</v>
       </c>
@@ -2829,18 +3253,28 @@
         <v>31</v>
       </c>
       <c r="O33" s="2"/>
-      <c r="P33" s="2">
+      <c r="P33" s="1">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="Q33" s="10" t="str">
         <f t="shared" si="6"/>
-        <v>7</v>
-      </c>
-      <c r="Q33" s="4" t="str">
-        <f>_xlfn.CONCAT(N33,"/","08/2019")</f>
-        <v>31/08/2019</v>
-      </c>
-      <c r="R33" s="4"/>
-      <c r="S33" s="4"/>
-    </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+        <v>31-08-2019</v>
+      </c>
+      <c r="R33" s="2">
+        <v>0</v>
+      </c>
+      <c r="S33" s="2">
+        <v>0</v>
+      </c>
+      <c r="T33" s="2">
+        <v>0</v>
+      </c>
+      <c r="U33" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>35</v>
       </c>
@@ -2890,18 +3324,28 @@
         <v>30</v>
       </c>
       <c r="O34" s="2"/>
-      <c r="P34" s="2">
+      <c r="P34" s="1">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="Q34" s="10" t="str">
         <f t="shared" si="6"/>
-        <v>7</v>
-      </c>
-      <c r="Q34" s="4" t="str">
-        <f>_xlfn.CONCAT(N34,"/","09/2019")</f>
-        <v>30/09/2019</v>
-      </c>
-      <c r="R34" s="4"/>
-      <c r="S34" s="4"/>
-    </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+        <v>30-09-2019</v>
+      </c>
+      <c r="R34" s="2">
+        <v>0</v>
+      </c>
+      <c r="S34" s="2">
+        <v>0</v>
+      </c>
+      <c r="T34" s="2">
+        <v>0</v>
+      </c>
+      <c r="U34" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>36</v>
       </c>
@@ -2951,18 +3395,28 @@
         <v>31</v>
       </c>
       <c r="O35" s="2"/>
-      <c r="P35" s="2">
+      <c r="P35" s="1">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="Q35" s="10" t="str">
         <f t="shared" si="6"/>
-        <v>7</v>
-      </c>
-      <c r="Q35" s="4" t="str">
-        <f>_xlfn.CONCAT(N35,"/","10/2019")</f>
-        <v>31/10/2019</v>
-      </c>
-      <c r="R35" s="4"/>
-      <c r="S35" s="4"/>
-    </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+        <v>31-10-2019</v>
+      </c>
+      <c r="R35" s="2">
+        <v>0</v>
+      </c>
+      <c r="S35" s="2">
+        <v>0</v>
+      </c>
+      <c r="T35" s="2">
+        <v>0</v>
+      </c>
+      <c r="U35" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>37</v>
       </c>
@@ -3012,18 +3466,28 @@
         <v>30</v>
       </c>
       <c r="O36" s="2"/>
-      <c r="P36" s="2">
+      <c r="P36" s="1">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="Q36" s="10" t="str">
         <f t="shared" si="6"/>
-        <v>7</v>
-      </c>
-      <c r="Q36" s="4" t="str">
-        <f>_xlfn.CONCAT(N36,"/","11/2019")</f>
-        <v>30/11/2019</v>
-      </c>
-      <c r="R36" s="4"/>
-      <c r="S36" s="4"/>
-    </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+        <v>30-11-2019</v>
+      </c>
+      <c r="R36" s="2">
+        <v>0</v>
+      </c>
+      <c r="S36" s="2">
+        <v>0</v>
+      </c>
+      <c r="T36" s="2">
+        <v>0</v>
+      </c>
+      <c r="U36" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>38</v>
       </c>
@@ -3073,18 +3537,28 @@
         <v>31</v>
       </c>
       <c r="O37" s="2"/>
-      <c r="P37" s="2">
+      <c r="P37" s="1">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="Q37" s="10" t="str">
         <f t="shared" si="6"/>
-        <v>7</v>
-      </c>
-      <c r="Q37" s="4" t="str">
-        <f>_xlfn.CONCAT(N37,"/","12/2019")</f>
-        <v>31/12/2019</v>
-      </c>
-      <c r="R37" s="4"/>
-      <c r="S37" s="4"/>
-    </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+        <v>31-12-2019</v>
+      </c>
+      <c r="R37" s="2">
+        <v>0</v>
+      </c>
+      <c r="S37" s="2">
+        <v>0</v>
+      </c>
+      <c r="T37" s="2">
+        <v>0</v>
+      </c>
+      <c r="U37" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>39</v>
       </c>
@@ -3134,18 +3608,28 @@
         <v>31</v>
       </c>
       <c r="O38" s="2"/>
-      <c r="P38" s="2">
+      <c r="P38" s="1">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="Q38" s="10" t="str">
         <f t="shared" si="6"/>
-        <v>7</v>
-      </c>
-      <c r="Q38" s="4" t="str">
-        <f>_xlfn.CONCAT(N38,"/","01/2020")</f>
-        <v>31/01/2020</v>
-      </c>
-      <c r="R38" s="4"/>
-      <c r="S38" s="4"/>
-    </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+        <v>31-01-2020</v>
+      </c>
+      <c r="R38" s="2">
+        <v>0</v>
+      </c>
+      <c r="S38" s="2">
+        <v>0</v>
+      </c>
+      <c r="T38" s="2">
+        <v>0</v>
+      </c>
+      <c r="U38" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>40</v>
       </c>
@@ -3195,18 +3679,28 @@
         <v>28</v>
       </c>
       <c r="O39" s="2"/>
-      <c r="P39" s="2">
+      <c r="P39" s="1">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="Q39" s="10" t="str">
         <f t="shared" si="6"/>
-        <v>7</v>
-      </c>
-      <c r="Q39" s="4" t="str">
-        <f>_xlfn.CONCAT(N39,"/","02/2020")</f>
-        <v>28/02/2020</v>
-      </c>
-      <c r="R39" s="4"/>
-      <c r="S39" s="4"/>
-    </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+        <v>28-02-2020</v>
+      </c>
+      <c r="R39" s="2">
+        <v>0</v>
+      </c>
+      <c r="S39" s="2">
+        <v>0</v>
+      </c>
+      <c r="T39" s="2">
+        <v>0</v>
+      </c>
+      <c r="U39" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>41</v>
       </c>
@@ -3256,18 +3750,28 @@
         <v>31</v>
       </c>
       <c r="O40" s="2"/>
-      <c r="P40" s="2">
+      <c r="P40" s="1">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="Q40" s="10" t="str">
         <f t="shared" si="6"/>
-        <v>7</v>
-      </c>
-      <c r="Q40" s="4" t="str">
-        <f>_xlfn.CONCAT(N40,"/","03/2020")</f>
-        <v>31/03/2020</v>
-      </c>
-      <c r="R40" s="4"/>
-      <c r="S40" s="4"/>
-    </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+        <v>31-03-2020</v>
+      </c>
+      <c r="R40" s="2">
+        <v>0</v>
+      </c>
+      <c r="S40" s="2">
+        <v>0</v>
+      </c>
+      <c r="T40" s="2">
+        <v>0</v>
+      </c>
+      <c r="U40" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>42</v>
       </c>
@@ -3317,18 +3821,28 @@
         <v>30</v>
       </c>
       <c r="O41" s="2"/>
-      <c r="P41" s="2">
+      <c r="P41" s="1">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="Q41" s="10" t="str">
         <f t="shared" si="6"/>
-        <v>7</v>
-      </c>
-      <c r="Q41" s="4" t="str">
-        <f>_xlfn.CONCAT(N41,"/","04/2020")</f>
-        <v>30/04/2020</v>
-      </c>
-      <c r="R41" s="4"/>
-      <c r="S41" s="4"/>
-    </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
+        <v>30-04-2020</v>
+      </c>
+      <c r="R41" s="2">
+        <v>0</v>
+      </c>
+      <c r="S41" s="2">
+        <v>0</v>
+      </c>
+      <c r="T41" s="2">
+        <v>0</v>
+      </c>
+      <c r="U41" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>43</v>
       </c>
@@ -3378,18 +3892,28 @@
         <v>31</v>
       </c>
       <c r="O42" s="2"/>
-      <c r="P42" s="2">
+      <c r="P42" s="1">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="Q42" s="10" t="str">
         <f t="shared" si="6"/>
-        <v>7</v>
-      </c>
-      <c r="Q42" s="4" t="str">
-        <f>_xlfn.CONCAT(N42,"/","05/2020")</f>
-        <v>31/05/2020</v>
-      </c>
-      <c r="R42" s="4"/>
-      <c r="S42" s="4"/>
-    </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+        <v>31-05-2020</v>
+      </c>
+      <c r="R42" s="2">
+        <v>0</v>
+      </c>
+      <c r="S42" s="2">
+        <v>0</v>
+      </c>
+      <c r="T42" s="2">
+        <v>0</v>
+      </c>
+      <c r="U42" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>44</v>
       </c>
@@ -3439,18 +3963,28 @@
         <v>30</v>
       </c>
       <c r="O43" s="2"/>
-      <c r="P43" s="2">
+      <c r="P43" s="1">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="Q43" s="10" t="str">
         <f t="shared" si="6"/>
-        <v>7</v>
-      </c>
-      <c r="Q43" s="4" t="str">
-        <f>_xlfn.CONCAT(N43,"/","06/2020")</f>
-        <v>30/06/2020</v>
-      </c>
-      <c r="R43" s="4"/>
-      <c r="S43" s="4"/>
-    </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
+        <v>30-06-2020</v>
+      </c>
+      <c r="R43" s="2">
+        <v>0</v>
+      </c>
+      <c r="S43" s="2">
+        <v>0</v>
+      </c>
+      <c r="T43" s="2">
+        <v>0</v>
+      </c>
+      <c r="U43" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>45</v>
       </c>
@@ -3500,18 +4034,28 @@
         <v>31</v>
       </c>
       <c r="O44" s="2"/>
-      <c r="P44" s="2">
+      <c r="P44" s="1">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="Q44" s="10" t="str">
         <f t="shared" si="6"/>
-        <v>7</v>
-      </c>
-      <c r="Q44" s="4" t="str">
-        <f>_xlfn.CONCAT(N44,"/","07/2020")</f>
-        <v>31/07/2020</v>
-      </c>
-      <c r="R44" s="4"/>
-      <c r="S44" s="4"/>
-    </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
+        <v>31-07-2020</v>
+      </c>
+      <c r="R44" s="2">
+        <v>0</v>
+      </c>
+      <c r="S44" s="2">
+        <v>0</v>
+      </c>
+      <c r="T44" s="2">
+        <v>0</v>
+      </c>
+      <c r="U44" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>46</v>
       </c>
@@ -3561,18 +4105,28 @@
         <v>31</v>
       </c>
       <c r="O45" s="2"/>
-      <c r="P45" s="2">
+      <c r="P45" s="1">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="Q45" s="10" t="str">
         <f t="shared" si="6"/>
-        <v>7</v>
-      </c>
-      <c r="Q45" s="4" t="str">
-        <f>_xlfn.CONCAT(N45,"/","08/2020")</f>
-        <v>31/08/2020</v>
-      </c>
-      <c r="R45" s="4"/>
-      <c r="S45" s="4"/>
-    </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
+        <v>31-08-2020</v>
+      </c>
+      <c r="R45" s="2">
+        <v>0</v>
+      </c>
+      <c r="S45" s="2">
+        <v>0</v>
+      </c>
+      <c r="T45" s="2">
+        <v>0</v>
+      </c>
+      <c r="U45" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>47</v>
       </c>
@@ -3622,18 +4176,28 @@
         <v>30</v>
       </c>
       <c r="O46" s="2"/>
-      <c r="P46" s="2">
+      <c r="P46" s="1">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="Q46" s="10" t="str">
         <f t="shared" si="6"/>
-        <v>7</v>
-      </c>
-      <c r="Q46" s="4" t="str">
-        <f>_xlfn.CONCAT(N46,"/","09/2020")</f>
-        <v>30/09/2020</v>
-      </c>
-      <c r="R46" s="4"/>
-      <c r="S46" s="4"/>
-    </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
+        <v>30-09-2020</v>
+      </c>
+      <c r="R46" s="2">
+        <v>0</v>
+      </c>
+      <c r="S46" s="2">
+        <v>0</v>
+      </c>
+      <c r="T46" s="2">
+        <v>0</v>
+      </c>
+      <c r="U46" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>48</v>
       </c>
@@ -3683,18 +4247,28 @@
         <v>31</v>
       </c>
       <c r="O47" s="2"/>
-      <c r="P47" s="2">
+      <c r="P47" s="1">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="Q47" s="10" t="str">
         <f t="shared" si="6"/>
-        <v>7</v>
-      </c>
-      <c r="Q47" s="4" t="str">
-        <f>_xlfn.CONCAT(N47,"/","10/2020")</f>
-        <v>31/10/2020</v>
-      </c>
-      <c r="R47" s="4"/>
-      <c r="S47" s="4"/>
-    </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
+        <v>31-10-2020</v>
+      </c>
+      <c r="R47" s="2">
+        <v>0</v>
+      </c>
+      <c r="S47" s="2">
+        <v>0</v>
+      </c>
+      <c r="T47" s="2">
+        <v>0</v>
+      </c>
+      <c r="U47" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>49</v>
       </c>
@@ -3744,18 +4318,28 @@
         <v>30</v>
       </c>
       <c r="O48" s="2"/>
-      <c r="P48" s="2">
+      <c r="P48" s="1">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="Q48" s="10" t="str">
         <f t="shared" si="6"/>
-        <v>7</v>
-      </c>
-      <c r="Q48" s="4" t="str">
-        <f>_xlfn.CONCAT(N48,"/","11/2020")</f>
-        <v>30/11/2020</v>
-      </c>
-      <c r="R48" s="4"/>
-      <c r="S48" s="4"/>
-    </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
+        <v>30-11-2020</v>
+      </c>
+      <c r="R48" s="2">
+        <v>0</v>
+      </c>
+      <c r="S48" s="2">
+        <v>0</v>
+      </c>
+      <c r="T48" s="2">
+        <v>0</v>
+      </c>
+      <c r="U48" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>50</v>
       </c>
@@ -3805,18 +4389,28 @@
         <v>31</v>
       </c>
       <c r="O49" s="2"/>
-      <c r="P49" s="2">
+      <c r="P49" s="1">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="Q49" s="10" t="str">
         <f t="shared" si="6"/>
-        <v>7</v>
-      </c>
-      <c r="Q49" s="4" t="str">
-        <f>_xlfn.CONCAT(N49,"/","12/2020")</f>
-        <v>31/12/2020</v>
-      </c>
-      <c r="R49" s="4"/>
-      <c r="S49" s="4"/>
-    </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
+        <v>31-12-2020</v>
+      </c>
+      <c r="R49" s="2">
+        <v>0</v>
+      </c>
+      <c r="S49" s="2">
+        <v>0</v>
+      </c>
+      <c r="T49" s="2">
+        <v>0</v>
+      </c>
+      <c r="U49" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>51</v>
       </c>
@@ -3866,18 +4460,28 @@
         <v>31</v>
       </c>
       <c r="O50" s="2"/>
-      <c r="P50" s="2">
+      <c r="P50" s="1">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="Q50" s="10" t="str">
         <f t="shared" si="6"/>
-        <v>7</v>
-      </c>
-      <c r="Q50" s="4" t="str">
-        <f>_xlfn.CONCAT(N50,"/","01/2021")</f>
-        <v>31/01/2021</v>
-      </c>
-      <c r="R50" s="4"/>
-      <c r="S50" s="4"/>
-    </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
+        <v>31-01-2021</v>
+      </c>
+      <c r="R50" s="2">
+        <v>0</v>
+      </c>
+      <c r="S50" s="2">
+        <v>0</v>
+      </c>
+      <c r="T50" s="2">
+        <v>0</v>
+      </c>
+      <c r="U50" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>52</v>
       </c>
@@ -3927,18 +4531,28 @@
         <v>28</v>
       </c>
       <c r="O51" s="2"/>
-      <c r="P51" s="2">
+      <c r="P51" s="1">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="Q51" s="10" t="str">
         <f t="shared" si="6"/>
-        <v>7</v>
-      </c>
-      <c r="Q51" s="4" t="str">
-        <f>_xlfn.CONCAT(N51,"/","02/2021")</f>
-        <v>28/02/2021</v>
-      </c>
-      <c r="R51" s="4"/>
-      <c r="S51" s="4"/>
-    </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
+        <v>28-02-2021</v>
+      </c>
+      <c r="R51" s="2">
+        <v>0</v>
+      </c>
+      <c r="S51" s="2">
+        <v>0</v>
+      </c>
+      <c r="T51" s="2">
+        <v>0</v>
+      </c>
+      <c r="U51" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>53</v>
       </c>
@@ -3988,18 +4602,28 @@
         <v>31</v>
       </c>
       <c r="O52" s="2"/>
-      <c r="P52" s="2">
+      <c r="P52" s="1">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="Q52" s="10" t="str">
         <f t="shared" si="6"/>
-        <v>7</v>
-      </c>
-      <c r="Q52" s="4" t="str">
-        <f>_xlfn.CONCAT(N52,"/","03/2021")</f>
-        <v>31/03/2021</v>
-      </c>
-      <c r="R52" s="4"/>
-      <c r="S52" s="4"/>
-    </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
+        <v>31-03-2021</v>
+      </c>
+      <c r="R52" s="2">
+        <v>0</v>
+      </c>
+      <c r="S52" s="2">
+        <v>0</v>
+      </c>
+      <c r="T52" s="2">
+        <v>0</v>
+      </c>
+      <c r="U52" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>54</v>
       </c>
@@ -4049,18 +4673,28 @@
         <v>30</v>
       </c>
       <c r="O53" s="2"/>
-      <c r="P53" s="2">
+      <c r="P53" s="1">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="Q53" s="10" t="str">
         <f t="shared" si="6"/>
-        <v>7</v>
-      </c>
-      <c r="Q53" s="4" t="str">
-        <f>_xlfn.CONCAT(N53,"/","04/2021")</f>
-        <v>30/04/2021</v>
-      </c>
-      <c r="R53" s="4"/>
-      <c r="S53" s="4"/>
-    </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
+        <v>30-04-2021</v>
+      </c>
+      <c r="R53" s="2">
+        <v>0</v>
+      </c>
+      <c r="S53" s="2">
+        <v>0</v>
+      </c>
+      <c r="T53" s="2">
+        <v>0</v>
+      </c>
+      <c r="U53" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>55</v>
       </c>
@@ -4110,18 +4744,28 @@
         <v>31</v>
       </c>
       <c r="O54" s="2"/>
-      <c r="P54" s="2">
+      <c r="P54" s="1">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="Q54" s="10" t="str">
         <f t="shared" si="6"/>
-        <v>7</v>
-      </c>
-      <c r="Q54" s="4" t="str">
-        <f>_xlfn.CONCAT(N54,"/","05/2021")</f>
-        <v>31/05/2021</v>
-      </c>
-      <c r="R54" s="4"/>
-      <c r="S54" s="4"/>
-    </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
+        <v>31-05-2021</v>
+      </c>
+      <c r="R54" s="2">
+        <v>0</v>
+      </c>
+      <c r="S54" s="2">
+        <v>0</v>
+      </c>
+      <c r="T54" s="2">
+        <v>0</v>
+      </c>
+      <c r="U54" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>56</v>
       </c>
@@ -4171,18 +4815,28 @@
         <v>30</v>
       </c>
       <c r="O55" s="2"/>
-      <c r="P55" s="2">
+      <c r="P55" s="1">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="Q55" s="10" t="str">
         <f t="shared" si="6"/>
-        <v>7</v>
-      </c>
-      <c r="Q55" s="4" t="str">
-        <f>_xlfn.CONCAT(N55,"/","06/2021")</f>
-        <v>30/06/2021</v>
-      </c>
-      <c r="R55" s="4"/>
-      <c r="S55" s="4"/>
-    </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
+        <v>30-06-2021</v>
+      </c>
+      <c r="R55" s="2">
+        <v>0</v>
+      </c>
+      <c r="S55" s="2">
+        <v>0</v>
+      </c>
+      <c r="T55" s="2">
+        <v>0</v>
+      </c>
+      <c r="U55" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>57</v>
       </c>
@@ -4232,18 +4886,28 @@
         <v>31</v>
       </c>
       <c r="O56" s="2"/>
-      <c r="P56" s="2">
+      <c r="P56" s="1">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="Q56" s="10" t="str">
         <f t="shared" si="6"/>
-        <v>7</v>
-      </c>
-      <c r="Q56" s="4" t="str">
-        <f>_xlfn.CONCAT(N56,"/","07/2021")</f>
-        <v>31/07/2021</v>
-      </c>
-      <c r="R56" s="4"/>
-      <c r="S56" s="4"/>
-    </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
+        <v>31-07-2021</v>
+      </c>
+      <c r="R56" s="2">
+        <v>0</v>
+      </c>
+      <c r="S56" s="2">
+        <v>0</v>
+      </c>
+      <c r="T56" s="2">
+        <v>0</v>
+      </c>
+      <c r="U56" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>58</v>
       </c>
@@ -4293,18 +4957,28 @@
         <v>31</v>
       </c>
       <c r="O57" s="2"/>
-      <c r="P57" s="2">
+      <c r="P57" s="1">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="Q57" s="10" t="str">
         <f t="shared" si="6"/>
-        <v>7</v>
-      </c>
-      <c r="Q57" s="4" t="str">
-        <f>_xlfn.CONCAT(N57,"/","08/2021")</f>
-        <v>31/08/2021</v>
-      </c>
-      <c r="R57" s="4"/>
-      <c r="S57" s="4"/>
-    </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
+        <v>31-08-2021</v>
+      </c>
+      <c r="R57" s="2">
+        <v>0</v>
+      </c>
+      <c r="S57" s="2">
+        <v>0</v>
+      </c>
+      <c r="T57" s="2">
+        <v>0</v>
+      </c>
+      <c r="U57" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>59</v>
       </c>
@@ -4354,18 +5028,28 @@
         <v>30</v>
       </c>
       <c r="O58" s="2"/>
-      <c r="P58" s="2">
+      <c r="P58" s="1">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="Q58" s="10" t="str">
         <f t="shared" si="6"/>
-        <v>7</v>
-      </c>
-      <c r="Q58" s="4" t="str">
-        <f>_xlfn.CONCAT(N58,"/","09/2021")</f>
-        <v>30/09/2021</v>
-      </c>
-      <c r="R58" s="4"/>
-      <c r="S58" s="4"/>
-    </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+        <v>30-09-2021</v>
+      </c>
+      <c r="R58" s="2">
+        <v>0</v>
+      </c>
+      <c r="S58" s="2">
+        <v>0</v>
+      </c>
+      <c r="T58" s="2">
+        <v>0</v>
+      </c>
+      <c r="U58" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>60</v>
       </c>
@@ -4415,18 +5099,28 @@
         <v>31</v>
       </c>
       <c r="O59" s="2"/>
-      <c r="P59" s="2">
+      <c r="P59" s="1">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="Q59" s="10" t="str">
         <f t="shared" si="6"/>
-        <v>7</v>
-      </c>
-      <c r="Q59" s="4" t="str">
-        <f>_xlfn.CONCAT(N59,"/","10/2021")</f>
-        <v>31/10/2021</v>
-      </c>
-      <c r="R59" s="4"/>
-      <c r="S59" s="4"/>
-    </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
+        <v>31-10-2021</v>
+      </c>
+      <c r="R59" s="2">
+        <v>0</v>
+      </c>
+      <c r="S59" s="2">
+        <v>0</v>
+      </c>
+      <c r="T59" s="2">
+        <v>0</v>
+      </c>
+      <c r="U59" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>61</v>
       </c>
@@ -4476,18 +5170,28 @@
         <v>30</v>
       </c>
       <c r="O60" s="2"/>
-      <c r="P60" s="2">
+      <c r="P60" s="1">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="Q60" s="10" t="str">
         <f t="shared" si="6"/>
-        <v>7</v>
-      </c>
-      <c r="Q60" s="4" t="str">
-        <f>_xlfn.CONCAT(N60,"/","11/2021")</f>
-        <v>30/11/2021</v>
-      </c>
-      <c r="R60" s="4"/>
-      <c r="S60" s="4"/>
-    </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
+        <v>30-11-2021</v>
+      </c>
+      <c r="R60" s="2">
+        <v>0</v>
+      </c>
+      <c r="S60" s="2">
+        <v>0</v>
+      </c>
+      <c r="T60" s="2">
+        <v>0</v>
+      </c>
+      <c r="U60" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>62</v>
       </c>
@@ -4537,18 +5241,28 @@
         <v>31</v>
       </c>
       <c r="O61" s="2"/>
-      <c r="P61" s="2">
+      <c r="P61" s="1">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="Q61" s="10" t="str">
         <f t="shared" si="6"/>
-        <v>7</v>
-      </c>
-      <c r="Q61" s="4" t="str">
-        <f>_xlfn.CONCAT(N61,"/","12/2021")</f>
-        <v>31/12/2021</v>
-      </c>
-      <c r="R61" s="4"/>
-      <c r="S61" s="4"/>
-    </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
+        <v>31-12-2021</v>
+      </c>
+      <c r="R61" s="2">
+        <v>0</v>
+      </c>
+      <c r="S61" s="2">
+        <v>0</v>
+      </c>
+      <c r="T61" s="2">
+        <v>0</v>
+      </c>
+      <c r="U61" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>63</v>
       </c>
@@ -4598,18 +5312,28 @@
         <v>31</v>
       </c>
       <c r="O62" s="2"/>
-      <c r="P62" s="2">
+      <c r="P62" s="1">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="Q62" s="10" t="str">
         <f t="shared" si="6"/>
-        <v>7</v>
-      </c>
-      <c r="Q62" s="4" t="str">
-        <f>_xlfn.CONCAT(N62,"/","01/2022")</f>
-        <v>31/01/2022</v>
-      </c>
-      <c r="R62" s="4"/>
-      <c r="S62" s="4"/>
-    </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
+        <v>31-01-2022</v>
+      </c>
+      <c r="R62" s="2">
+        <v>0</v>
+      </c>
+      <c r="S62" s="2">
+        <v>0</v>
+      </c>
+      <c r="T62" s="2">
+        <v>0</v>
+      </c>
+      <c r="U62" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>64</v>
       </c>
@@ -4659,18 +5383,28 @@
         <v>28</v>
       </c>
       <c r="O63" s="2"/>
-      <c r="P63" s="2">
+      <c r="P63" s="1">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="Q63" s="10" t="str">
         <f t="shared" si="6"/>
-        <v>7</v>
-      </c>
-      <c r="Q63" s="4" t="str">
-        <f>_xlfn.CONCAT(N63,"/","02/2022")</f>
-        <v>28/02/2022</v>
-      </c>
-      <c r="R63" s="4"/>
-      <c r="S63" s="4"/>
-    </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
+        <v>28-02-2022</v>
+      </c>
+      <c r="R63" s="2">
+        <v>0</v>
+      </c>
+      <c r="S63" s="2">
+        <v>0</v>
+      </c>
+      <c r="T63" s="2">
+        <v>0</v>
+      </c>
+      <c r="U63" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>65</v>
       </c>
@@ -4720,18 +5454,28 @@
         <v>31</v>
       </c>
       <c r="O64" s="2"/>
-      <c r="P64" s="2">
+      <c r="P64" s="1">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="Q64" s="10" t="str">
         <f t="shared" si="6"/>
-        <v>7</v>
-      </c>
-      <c r="Q64" s="4" t="str">
-        <f>_xlfn.CONCAT(N64,"/","03/2022")</f>
-        <v>31/03/2022</v>
-      </c>
-      <c r="R64" s="4"/>
-      <c r="S64" s="4"/>
-    </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
+        <v>31-03-2022</v>
+      </c>
+      <c r="R64" s="2">
+        <v>0</v>
+      </c>
+      <c r="S64" s="2">
+        <v>0</v>
+      </c>
+      <c r="T64" s="2">
+        <v>0</v>
+      </c>
+      <c r="U64" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>66</v>
       </c>
@@ -4781,18 +5525,28 @@
         <v>30</v>
       </c>
       <c r="O65" s="2"/>
-      <c r="P65" s="2">
+      <c r="P65" s="1">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="Q65" s="10" t="str">
         <f t="shared" si="6"/>
-        <v>7</v>
-      </c>
-      <c r="Q65" s="4" t="str">
-        <f>_xlfn.CONCAT(N65,"/","04/2022")</f>
-        <v>30/04/2022</v>
-      </c>
-      <c r="R65" s="4"/>
-      <c r="S65" s="4"/>
-    </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
+        <v>30-04-2022</v>
+      </c>
+      <c r="R65" s="2">
+        <v>0</v>
+      </c>
+      <c r="S65" s="2">
+        <v>0</v>
+      </c>
+      <c r="T65" s="2">
+        <v>0</v>
+      </c>
+      <c r="U65" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>67</v>
       </c>
@@ -4842,18 +5596,28 @@
         <v>31</v>
       </c>
       <c r="O66" s="2"/>
-      <c r="P66" s="2">
+      <c r="P66" s="1">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="Q66" s="10" t="str">
         <f t="shared" si="6"/>
-        <v>7</v>
-      </c>
-      <c r="Q66" s="4" t="str">
-        <f>_xlfn.CONCAT(N66,"/","05/2022")</f>
-        <v>31/05/2022</v>
-      </c>
-      <c r="R66" s="4"/>
-      <c r="S66" s="4"/>
-    </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
+        <v>31-05-2022</v>
+      </c>
+      <c r="R66" s="2">
+        <v>0</v>
+      </c>
+      <c r="S66" s="2">
+        <v>0</v>
+      </c>
+      <c r="T66" s="2">
+        <v>0</v>
+      </c>
+      <c r="U66" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>68</v>
       </c>
@@ -4864,36 +5628,36 @@
         <v>81.599999999999994</v>
       </c>
       <c r="D67" s="1">
-        <f t="shared" ref="D67:D113" si="7">ROUND(B67*C67,0)</f>
+        <f t="shared" ref="D67:D121" si="8">ROUND(B67*C67,0)</f>
         <v>2699885</v>
       </c>
       <c r="E67" s="2">
         <v>122.6</v>
       </c>
       <c r="F67" s="1">
-        <f t="shared" ref="F67:F113" si="8">ROUND(B67*E67,0)</f>
+        <f t="shared" ref="F67:F121" si="9">ROUND(B67*E67,0)</f>
         <v>4056445</v>
       </c>
       <c r="G67" s="2">
         <v>1.86</v>
       </c>
       <c r="H67" s="1">
-        <f t="shared" ref="H67:H113" si="9">G67/100</f>
+        <f t="shared" ref="H67:H113" si="10">G67/100</f>
         <v>1.8600000000000002E-2</v>
       </c>
       <c r="I67" s="1">
-        <f t="shared" ref="I67:I113" si="10">+C67*0.07</f>
+        <f t="shared" ref="I67:I113" si="11">+C67*0.07</f>
         <v>5.7119999999999997</v>
       </c>
       <c r="J67" s="1">
-        <f t="shared" ref="J67:J113" si="11">ROUND(B67*I67,0)</f>
+        <f t="shared" ref="J67:J113" si="12">ROUND(B67*I67,0)</f>
         <v>188992</v>
       </c>
       <c r="K67" s="2">
         <v>380000</v>
       </c>
       <c r="L67" s="3">
-        <f t="shared" ref="L67:L113" si="12">ROUND((K67*4.75)/12,0)</f>
+        <f t="shared" ref="L67:L121" si="13">ROUND((K67*4.75)/12,0)</f>
         <v>150417</v>
       </c>
       <c r="M67" s="2">
@@ -4903,18 +5667,28 @@
         <v>30</v>
       </c>
       <c r="O67" s="2"/>
-      <c r="P67" s="2">
-        <f t="shared" si="6"/>
+      <c r="P67" s="1">
+        <f t="shared" si="7"/>
         <v>7</v>
       </c>
-      <c r="Q67" s="4" t="str">
-        <f>_xlfn.CONCAT(N67,"/","06/2022")</f>
-        <v>30/06/2022</v>
-      </c>
-      <c r="R67" s="4"/>
-      <c r="S67" s="4"/>
-    </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q67" s="10" t="str">
+        <f t="shared" ref="Q67:Q97" si="14">_xlfn.CONCAT(N67,"-",RIGHT(A67,2),"-",LEFT(A67,4))</f>
+        <v>30-06-2022</v>
+      </c>
+      <c r="R67" s="2">
+        <v>0</v>
+      </c>
+      <c r="S67" s="2">
+        <v>0</v>
+      </c>
+      <c r="T67" s="2">
+        <v>0</v>
+      </c>
+      <c r="U67" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>69</v>
       </c>
@@ -4925,36 +5699,36 @@
         <v>81.599999999999994</v>
       </c>
       <c r="D68" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2726848</v>
       </c>
       <c r="E68" s="2">
         <v>122.6</v>
       </c>
       <c r="F68" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4096956</v>
       </c>
       <c r="G68" s="2">
         <v>1.84</v>
       </c>
       <c r="H68" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.84E-2</v>
       </c>
       <c r="I68" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5.7119999999999997</v>
       </c>
       <c r="J68" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>190879</v>
       </c>
       <c r="K68" s="2">
         <v>380000</v>
       </c>
       <c r="L68" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>150417</v>
       </c>
       <c r="M68" s="2">
@@ -4966,17 +5740,27 @@
       <c r="O68" s="2">
         <v>6.45</v>
       </c>
-      <c r="P68" s="2">
+      <c r="P68" s="1">
         <v>0.55000000000000004</v>
       </c>
-      <c r="Q68" s="4" t="str">
-        <f>_xlfn.CONCAT(N68,"/","07/2022")</f>
-        <v>31/07/2022</v>
-      </c>
-      <c r="R68" s="4"/>
-      <c r="S68" s="4"/>
-    </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q68" s="10" t="str">
+        <f t="shared" si="14"/>
+        <v>31-07-2022</v>
+      </c>
+      <c r="R68" s="2">
+        <v>0</v>
+      </c>
+      <c r="S68" s="2">
+        <v>0</v>
+      </c>
+      <c r="T68" s="2">
+        <v>0</v>
+      </c>
+      <c r="U68" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>70</v>
       </c>
@@ -4987,36 +5771,36 @@
         <v>81.599999999999994</v>
       </c>
       <c r="D69" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2761059</v>
       </c>
       <c r="E69" s="2">
         <v>122.6</v>
       </c>
       <c r="F69" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4148356</v>
       </c>
       <c r="G69" s="2">
         <v>1.84</v>
       </c>
       <c r="H69" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.84E-2</v>
       </c>
       <c r="I69" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5.7119999999999997</v>
       </c>
       <c r="J69" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>193274</v>
       </c>
       <c r="K69" s="2">
         <v>400000</v>
       </c>
       <c r="L69" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>158333</v>
       </c>
       <c r="M69" s="2">
@@ -5028,17 +5812,27 @@
       <c r="O69" s="2">
         <v>6.45</v>
       </c>
-      <c r="P69" s="2">
+      <c r="P69" s="1">
         <v>0.55000000000000004</v>
       </c>
-      <c r="Q69" s="4" t="str">
-        <f>_xlfn.CONCAT(N69,"/","08/2022")</f>
-        <v>31/08/2022</v>
-      </c>
-      <c r="R69" s="4"/>
-      <c r="S69" s="4"/>
-    </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q69" s="10" t="str">
+        <f t="shared" si="14"/>
+        <v>31-08-2022</v>
+      </c>
+      <c r="R69" s="2">
+        <v>0</v>
+      </c>
+      <c r="S69" s="2">
+        <v>0</v>
+      </c>
+      <c r="T69" s="2">
+        <v>0</v>
+      </c>
+      <c r="U69" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>71</v>
       </c>
@@ -5049,36 +5843,36 @@
         <v>81.599999999999994</v>
       </c>
       <c r="D70" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2795472</v>
       </c>
       <c r="E70" s="2">
         <v>122.6</v>
       </c>
       <c r="F70" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4200059</v>
       </c>
       <c r="G70" s="2">
         <v>1.84</v>
       </c>
       <c r="H70" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.84E-2</v>
       </c>
       <c r="I70" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5.7119999999999997</v>
       </c>
       <c r="J70" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>195683</v>
       </c>
       <c r="K70" s="2">
         <v>400000</v>
       </c>
       <c r="L70" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>158333</v>
       </c>
       <c r="M70" s="2">
@@ -5090,17 +5884,27 @@
       <c r="O70" s="2">
         <v>6.45</v>
       </c>
-      <c r="P70" s="2">
+      <c r="P70" s="1">
         <v>0.55000000000000004</v>
       </c>
-      <c r="Q70" s="4" t="str">
-        <f>_xlfn.CONCAT(N70,"/","09/2022")</f>
-        <v>30/09/2022</v>
-      </c>
-      <c r="R70" s="4"/>
-      <c r="S70" s="4"/>
-    </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q70" s="10" t="str">
+        <f t="shared" si="14"/>
+        <v>30-09-2022</v>
+      </c>
+      <c r="R70" s="2">
+        <v>0</v>
+      </c>
+      <c r="S70" s="2">
+        <v>0</v>
+      </c>
+      <c r="T70" s="2">
+        <v>0</v>
+      </c>
+      <c r="U70" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>72</v>
       </c>
@@ -5111,36 +5915,36 @@
         <v>81.599999999999994</v>
       </c>
       <c r="D71" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2823389</v>
       </c>
       <c r="E71" s="2">
         <v>122.6</v>
       </c>
       <c r="F71" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4242003</v>
       </c>
       <c r="G71" s="2">
         <v>1.54</v>
       </c>
       <c r="H71" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.54E-2</v>
       </c>
       <c r="I71" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5.7119999999999997</v>
       </c>
       <c r="J71" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>197637</v>
       </c>
       <c r="K71" s="2">
         <v>400000</v>
       </c>
       <c r="L71" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>158333</v>
       </c>
       <c r="M71" s="2">
@@ -5152,17 +5956,27 @@
       <c r="O71" s="2">
         <v>6.45</v>
       </c>
-      <c r="P71" s="2">
+      <c r="P71" s="1">
         <v>0.55000000000000004</v>
       </c>
-      <c r="Q71" s="4" t="str">
-        <f>_xlfn.CONCAT(N71,"/","10/2022")</f>
-        <v>31/10/2022</v>
-      </c>
-      <c r="R71" s="4"/>
-      <c r="S71" s="4"/>
-    </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q71" s="10" t="str">
+        <f t="shared" si="14"/>
+        <v>31-10-2022</v>
+      </c>
+      <c r="R71" s="2">
+        <v>0</v>
+      </c>
+      <c r="S71" s="2">
+        <v>0</v>
+      </c>
+      <c r="T71" s="2">
+        <v>0</v>
+      </c>
+      <c r="U71" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>73</v>
       </c>
@@ -5173,36 +5987,36 @@
         <v>81.599999999999994</v>
       </c>
       <c r="D72" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2840643</v>
       </c>
       <c r="E72" s="2">
         <v>122.6</v>
       </c>
       <c r="F72" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4267927</v>
       </c>
       <c r="G72" s="2">
         <v>1.54</v>
       </c>
       <c r="H72" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.54E-2</v>
       </c>
       <c r="I72" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5.7119999999999997</v>
       </c>
       <c r="J72" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>198845</v>
       </c>
       <c r="K72" s="2">
         <v>400000</v>
       </c>
       <c r="L72" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>158333</v>
       </c>
       <c r="M72" s="2">
@@ -5214,17 +6028,27 @@
       <c r="O72" s="2">
         <v>6.45</v>
       </c>
-      <c r="P72" s="2">
+      <c r="P72" s="1">
         <v>0.55000000000000004</v>
       </c>
-      <c r="Q72" s="4" t="str">
-        <f>_xlfn.CONCAT(N72,"/","11/2022")</f>
-        <v>30/11/2022</v>
-      </c>
-      <c r="R72" s="4"/>
-      <c r="S72" s="4"/>
-    </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q72" s="10" t="str">
+        <f t="shared" si="14"/>
+        <v>30-11-2022</v>
+      </c>
+      <c r="R72" s="2">
+        <v>0</v>
+      </c>
+      <c r="S72" s="2">
+        <v>0</v>
+      </c>
+      <c r="T72" s="2">
+        <v>0</v>
+      </c>
+      <c r="U72" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>74</v>
       </c>
@@ -5235,36 +6059,36 @@
         <v>81.599999999999994</v>
       </c>
       <c r="D73" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2865056</v>
       </c>
       <c r="E73" s="2">
         <v>122.6</v>
       </c>
       <c r="F73" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4304606</v>
       </c>
       <c r="G73" s="2">
         <v>1.54</v>
       </c>
       <c r="H73" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.54E-2</v>
       </c>
       <c r="I73" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5.7119999999999997</v>
       </c>
       <c r="J73" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>200554</v>
       </c>
       <c r="K73" s="2">
         <v>400000</v>
       </c>
       <c r="L73" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>158333</v>
       </c>
       <c r="M73" s="2">
@@ -5276,17 +6100,27 @@
       <c r="O73" s="2">
         <v>6.45</v>
       </c>
-      <c r="P73" s="2">
+      <c r="P73" s="1">
         <v>0.55000000000000004</v>
       </c>
-      <c r="Q73" s="4" t="str">
-        <f>_xlfn.CONCAT(N73,"/","12/2022")</f>
-        <v>31/12/2022</v>
-      </c>
-      <c r="R73" s="4"/>
-      <c r="S73" s="4"/>
-    </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q73" s="10" t="str">
+        <f t="shared" si="14"/>
+        <v>31-12-2022</v>
+      </c>
+      <c r="R73" s="2">
+        <v>0</v>
+      </c>
+      <c r="S73" s="2">
+        <v>0</v>
+      </c>
+      <c r="T73" s="2">
+        <v>0</v>
+      </c>
+      <c r="U73" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>75</v>
       </c>
@@ -5297,36 +6131,36 @@
         <v>81.599999999999994</v>
       </c>
       <c r="D74" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2879460</v>
       </c>
       <c r="E74" s="2">
         <v>122.6</v>
       </c>
       <c r="F74" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4326248</v>
       </c>
       <c r="G74" s="2">
         <v>1.55</v>
       </c>
       <c r="H74" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.55E-2</v>
       </c>
       <c r="I74" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5.7119999999999997</v>
       </c>
       <c r="J74" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>201562</v>
       </c>
       <c r="K74" s="2">
         <v>410000</v>
       </c>
       <c r="L74" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>162292</v>
       </c>
       <c r="M74" s="2">
@@ -5338,18 +6172,28 @@
       <c r="O74" s="2">
         <v>3.1</v>
       </c>
-      <c r="P74" s="2">
+      <c r="P74" s="1">
         <f>7-O74</f>
         <v>3.9</v>
       </c>
-      <c r="Q74" s="4" t="str">
-        <f>_xlfn.CONCAT(N74,"/","01/2023")</f>
-        <v>31/01/2023</v>
-      </c>
-      <c r="R74" s="4"/>
-      <c r="S74" s="4"/>
-    </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q74" s="10" t="str">
+        <f t="shared" si="14"/>
+        <v>31-01-2023</v>
+      </c>
+      <c r="R74" s="2">
+        <v>0</v>
+      </c>
+      <c r="S74" s="2">
+        <v>0</v>
+      </c>
+      <c r="T74" s="2">
+        <v>0</v>
+      </c>
+      <c r="U74" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>76</v>
       </c>
@@ -5360,36 +6204,36 @@
         <v>81.599999999999994</v>
       </c>
       <c r="D75" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2897590</v>
       </c>
       <c r="E75" s="2">
         <v>122.6</v>
       </c>
       <c r="F75" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4353487</v>
       </c>
       <c r="G75" s="2">
         <v>1.55</v>
       </c>
       <c r="H75" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.55E-2</v>
       </c>
       <c r="I75" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5.7119999999999997</v>
       </c>
       <c r="J75" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>202831</v>
       </c>
       <c r="K75" s="2">
         <v>410000</v>
       </c>
       <c r="L75" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>162292</v>
       </c>
       <c r="M75" s="2">
@@ -5401,18 +6245,28 @@
       <c r="O75" s="2">
         <v>6</v>
       </c>
-      <c r="P75" s="2">
-        <f t="shared" ref="P75:P113" si="13">7-O75</f>
+      <c r="P75" s="1">
+        <f t="shared" ref="P75:P138" si="15">7-O75</f>
         <v>1</v>
       </c>
-      <c r="Q75" s="4" t="str">
-        <f>_xlfn.CONCAT(N75,"/","02/2023")</f>
-        <v>28/02/2023</v>
-      </c>
-      <c r="R75" s="4"/>
-      <c r="S75" s="4"/>
-    </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q75" s="10" t="str">
+        <f t="shared" si="14"/>
+        <v>28-02-2023</v>
+      </c>
+      <c r="R75" s="2">
+        <v>0</v>
+      </c>
+      <c r="S75" s="2">
+        <v>0</v>
+      </c>
+      <c r="T75" s="2">
+        <v>0</v>
+      </c>
+      <c r="U75" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>77</v>
       </c>
@@ -5423,36 +6277,36 @@
         <v>81.599999999999994</v>
       </c>
       <c r="D76" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2902959</v>
       </c>
       <c r="E76" s="2">
         <v>122.6</v>
       </c>
       <c r="F76" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4361554</v>
       </c>
       <c r="G76" s="2">
         <v>1.55</v>
       </c>
       <c r="H76" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.55E-2</v>
       </c>
       <c r="I76" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5.7119999999999997</v>
       </c>
       <c r="J76" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>203207</v>
       </c>
       <c r="K76" s="2">
         <v>410000</v>
       </c>
       <c r="L76" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>162292</v>
       </c>
       <c r="M76" s="2">
@@ -5464,18 +6318,28 @@
       <c r="O76" s="2">
         <v>6</v>
       </c>
-      <c r="P76" s="2">
-        <f t="shared" si="13"/>
+      <c r="P76" s="1">
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="Q76" s="4" t="str">
-        <f>_xlfn.CONCAT(N76,"/","03/2023")</f>
-        <v>31/03/2023</v>
-      </c>
-      <c r="R76" s="4"/>
-      <c r="S76" s="4"/>
-    </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q76" s="10" t="str">
+        <f t="shared" si="14"/>
+        <v>31-03-2023</v>
+      </c>
+      <c r="R76" s="2">
+        <v>0</v>
+      </c>
+      <c r="S76" s="2">
+        <v>0</v>
+      </c>
+      <c r="T76" s="2">
+        <v>0</v>
+      </c>
+      <c r="U76" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>78</v>
       </c>
@@ -5486,36 +6350,36 @@
         <v>81.599999999999994</v>
       </c>
       <c r="D77" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2924426</v>
       </c>
       <c r="E77" s="2">
         <v>122.6</v>
       </c>
       <c r="F77" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4393806</v>
       </c>
       <c r="G77" s="2">
         <v>1.61</v>
       </c>
       <c r="H77" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.61E-2</v>
       </c>
       <c r="I77" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5.7119999999999997</v>
       </c>
       <c r="J77" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>204710</v>
       </c>
       <c r="K77" s="2">
         <v>410000</v>
       </c>
       <c r="L77" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>162292</v>
       </c>
       <c r="M77" s="2">
@@ -5527,18 +6391,28 @@
       <c r="O77" s="2">
         <v>6</v>
       </c>
-      <c r="P77" s="2">
-        <f t="shared" si="13"/>
+      <c r="P77" s="1">
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="Q77" s="4" t="str">
-        <f>_xlfn.CONCAT(N77,"/","04/2023")</f>
-        <v>30/04/2023</v>
-      </c>
-      <c r="R77" s="4"/>
-      <c r="S77" s="4"/>
-    </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q77" s="10" t="str">
+        <f t="shared" si="14"/>
+        <v>30-04-2023</v>
+      </c>
+      <c r="R77" s="2">
+        <v>0</v>
+      </c>
+      <c r="S77" s="2">
+        <v>0</v>
+      </c>
+      <c r="T77" s="2">
+        <v>0</v>
+      </c>
+      <c r="U77" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>79</v>
       </c>
@@ -5549,36 +6423,36 @@
         <v>81.599999999999994</v>
       </c>
       <c r="D78" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2940284</v>
       </c>
       <c r="E78" s="2">
         <v>122.6</v>
       </c>
       <c r="F78" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4417632</v>
       </c>
       <c r="G78" s="2">
         <v>1.61</v>
       </c>
       <c r="H78" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.61E-2</v>
       </c>
       <c r="I78" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5.7119999999999997</v>
       </c>
       <c r="J78" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>205820</v>
       </c>
       <c r="K78" s="2">
         <v>440000</v>
       </c>
       <c r="L78" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>174167</v>
       </c>
       <c r="M78" s="2">
@@ -5590,18 +6464,28 @@
       <c r="O78" s="2">
         <v>6</v>
       </c>
-      <c r="P78" s="2">
-        <f t="shared" si="13"/>
+      <c r="P78" s="1">
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="Q78" s="4" t="str">
-        <f>_xlfn.CONCAT(N78,"/","05/2023")</f>
-        <v>31/05/2023</v>
-      </c>
-      <c r="R78" s="4"/>
-      <c r="S78" s="4"/>
-    </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q78" s="10" t="str">
+        <f t="shared" si="14"/>
+        <v>31-05-2023</v>
+      </c>
+      <c r="R78" s="2">
+        <v>0</v>
+      </c>
+      <c r="S78" s="2">
+        <v>0</v>
+      </c>
+      <c r="T78" s="2">
+        <v>0</v>
+      </c>
+      <c r="U78" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>80</v>
       </c>
@@ -5612,36 +6496,36 @@
         <v>81.599999999999994</v>
       </c>
       <c r="D79" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2944902</v>
       </c>
       <c r="E79" s="2">
         <v>122.6</v>
       </c>
       <c r="F79" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4424570</v>
       </c>
       <c r="G79" s="2">
         <v>1.61</v>
       </c>
       <c r="H79" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.61E-2</v>
       </c>
       <c r="I79" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5.7119999999999997</v>
       </c>
       <c r="J79" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>206143</v>
       </c>
       <c r="K79" s="2">
         <v>440000</v>
       </c>
       <c r="L79" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>174167</v>
       </c>
       <c r="M79" s="2">
@@ -5653,18 +6537,28 @@
       <c r="O79" s="2">
         <v>6</v>
       </c>
-      <c r="P79" s="2">
-        <f t="shared" si="13"/>
+      <c r="P79" s="1">
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="Q79" s="4" t="str">
-        <f>_xlfn.CONCAT(N79,"/","06/2023")</f>
-        <v>30/06/2023</v>
-      </c>
-      <c r="R79" s="4"/>
-      <c r="S79" s="4"/>
-    </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q79" s="10" t="str">
+        <f t="shared" si="14"/>
+        <v>30-06-2023</v>
+      </c>
+      <c r="R79" s="2">
+        <v>0</v>
+      </c>
+      <c r="S79" s="2">
+        <v>0</v>
+      </c>
+      <c r="T79" s="2">
+        <v>0</v>
+      </c>
+      <c r="U79" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>81</v>
       </c>
@@ -5675,36 +6569,36 @@
         <v>81.599999999999994</v>
       </c>
       <c r="D80" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2941602</v>
       </c>
       <c r="E80" s="2">
         <v>122.6</v>
       </c>
       <c r="F80" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4419614</v>
       </c>
       <c r="G80" s="2">
         <v>1.88</v>
       </c>
       <c r="H80" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.8799999999999997E-2</v>
       </c>
       <c r="I80" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5.7119999999999997</v>
       </c>
       <c r="J80" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>205912</v>
       </c>
       <c r="K80" s="2">
         <v>440000</v>
       </c>
       <c r="L80" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>174167</v>
       </c>
       <c r="M80" s="2">
@@ -5716,18 +6610,28 @@
       <c r="O80" s="2">
         <v>6</v>
       </c>
-      <c r="P80" s="2">
-        <f t="shared" si="13"/>
+      <c r="P80" s="1">
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="Q80" s="4" t="str">
-        <f>_xlfn.CONCAT(N80,"/","07/2023")</f>
-        <v>31/07/2023</v>
-      </c>
-      <c r="R80" s="4"/>
-      <c r="S80" s="4"/>
-    </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q80" s="10" t="str">
+        <f t="shared" si="14"/>
+        <v>31-07-2023</v>
+      </c>
+      <c r="R80" s="2">
+        <v>0</v>
+      </c>
+      <c r="S80" s="2">
+        <v>0</v>
+      </c>
+      <c r="T80" s="2">
+        <v>0</v>
+      </c>
+      <c r="U80" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>82</v>
       </c>
@@ -5738,36 +6642,36 @@
         <v>81.599999999999994</v>
       </c>
       <c r="D81" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2948233</v>
       </c>
       <c r="E81" s="2">
         <v>122.6</v>
       </c>
       <c r="F81" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4429576</v>
       </c>
       <c r="G81" s="2">
         <v>1.88</v>
       </c>
       <c r="H81" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.8799999999999997E-2</v>
       </c>
       <c r="I81" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5.7119999999999997</v>
       </c>
       <c r="J81" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>206376</v>
       </c>
       <c r="K81" s="2">
         <v>440000</v>
       </c>
       <c r="L81" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>174167</v>
       </c>
       <c r="M81" s="2">
@@ -5779,18 +6683,28 @@
       <c r="O81" s="2">
         <v>6</v>
       </c>
-      <c r="P81" s="2">
-        <f t="shared" si="13"/>
+      <c r="P81" s="1">
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="Q81" s="4" t="str">
-        <f>_xlfn.CONCAT(N81,"/","08/2023")</f>
-        <v>31/08/2023</v>
-      </c>
-      <c r="R81" s="4"/>
-      <c r="S81" s="4"/>
-    </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q81" s="10" t="str">
+        <f t="shared" si="14"/>
+        <v>31-08-2023</v>
+      </c>
+      <c r="R81" s="2">
+        <v>0</v>
+      </c>
+      <c r="S81" s="2">
+        <v>0</v>
+      </c>
+      <c r="T81" s="2">
+        <v>0</v>
+      </c>
+      <c r="U81" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>83</v>
       </c>
@@ -5801,36 +6715,36 @@
         <v>81.599999999999994</v>
       </c>
       <c r="D82" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2953718</v>
       </c>
       <c r="E82" s="2">
         <v>122.6</v>
       </c>
       <c r="F82" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4437817</v>
       </c>
       <c r="G82" s="2">
         <v>1.88</v>
       </c>
       <c r="H82" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.8799999999999997E-2</v>
       </c>
       <c r="I82" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5.7119999999999997</v>
       </c>
       <c r="J82" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>206760</v>
       </c>
       <c r="K82" s="2">
         <v>460000</v>
       </c>
       <c r="L82" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>182083</v>
       </c>
       <c r="M82" s="2">
@@ -5842,18 +6756,28 @@
       <c r="O82" s="2">
         <v>6</v>
       </c>
-      <c r="P82" s="2">
-        <f t="shared" si="13"/>
+      <c r="P82" s="1">
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="Q82" s="4" t="str">
-        <f>_xlfn.CONCAT(N82,"/","09/2023")</f>
-        <v>30/09/2023</v>
-      </c>
-      <c r="R82" s="4"/>
-      <c r="S82" s="4"/>
-    </row>
-    <row r="83" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q82" s="10" t="str">
+        <f t="shared" si="14"/>
+        <v>30-09-2023</v>
+      </c>
+      <c r="R82" s="2">
+        <v>0</v>
+      </c>
+      <c r="S82" s="2">
+        <v>0</v>
+      </c>
+      <c r="T82" s="2">
+        <v>0</v>
+      </c>
+      <c r="U82" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>84</v>
       </c>
@@ -5864,36 +6788,36 @@
         <v>81.599999999999994</v>
       </c>
       <c r="D83" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2969267</v>
       </c>
       <c r="E83" s="2">
         <v>122.6</v>
       </c>
       <c r="F83" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4461177</v>
       </c>
       <c r="G83" s="2">
         <v>1.47</v>
       </c>
       <c r="H83" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.47E-2</v>
       </c>
       <c r="I83" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5.7119999999999997</v>
       </c>
       <c r="J83" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>207849</v>
       </c>
       <c r="K83" s="2">
         <v>460000</v>
       </c>
       <c r="L83" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>182083</v>
       </c>
       <c r="M83" s="2">
@@ -5905,18 +6829,28 @@
       <c r="O83" s="2">
         <v>6</v>
       </c>
-      <c r="P83" s="2">
-        <f t="shared" si="13"/>
+      <c r="P83" s="1">
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="Q83" s="4" t="str">
-        <f>_xlfn.CONCAT(N83,"/","10/2023")</f>
-        <v>31/10/2023</v>
-      </c>
-      <c r="R83" s="4"/>
-      <c r="S83" s="4"/>
-    </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q83" s="10" t="str">
+        <f t="shared" si="14"/>
+        <v>31-10-2023</v>
+      </c>
+      <c r="R83" s="2">
+        <v>0</v>
+      </c>
+      <c r="S83" s="2">
+        <v>0</v>
+      </c>
+      <c r="T83" s="2">
+        <v>0</v>
+      </c>
+      <c r="U83" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>85</v>
       </c>
@@ -5927,36 +6861,36 @@
         <v>81.599999999999994</v>
       </c>
       <c r="D84" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2983612</v>
       </c>
       <c r="E84" s="2">
         <v>122.6</v>
       </c>
       <c r="F84" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4482730</v>
       </c>
       <c r="G84" s="2">
         <v>1.47</v>
       </c>
       <c r="H84" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.47E-2</v>
       </c>
       <c r="I84" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5.7119999999999997</v>
       </c>
       <c r="J84" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>208853</v>
       </c>
       <c r="K84" s="2">
         <v>460000</v>
       </c>
       <c r="L84" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>182083</v>
       </c>
       <c r="M84" s="2">
@@ -5968,18 +6902,28 @@
       <c r="O84" s="2">
         <v>6</v>
       </c>
-      <c r="P84" s="2">
-        <f t="shared" si="13"/>
+      <c r="P84" s="1">
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="Q84" s="4" t="str">
-        <f>_xlfn.CONCAT(N84,"/","11/2023")</f>
-        <v>30/11/2023</v>
-      </c>
-      <c r="R84" s="4"/>
-      <c r="S84" s="4"/>
-    </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q84" s="10" t="str">
+        <f t="shared" si="14"/>
+        <v>30-11-2023</v>
+      </c>
+      <c r="R84" s="2">
+        <v>0</v>
+      </c>
+      <c r="S84" s="2">
+        <v>0</v>
+      </c>
+      <c r="T84" s="2">
+        <v>0</v>
+      </c>
+      <c r="U84" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>86</v>
       </c>
@@ -5990,36 +6934,36 @@
         <v>81.599999999999994</v>
       </c>
       <c r="D85" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3002012</v>
       </c>
       <c r="E85" s="2">
         <v>122.6</v>
       </c>
       <c r="F85" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4510376</v>
       </c>
       <c r="G85" s="2">
         <v>1.47</v>
       </c>
       <c r="H85" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.47E-2</v>
       </c>
       <c r="I85" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5.7119999999999997</v>
       </c>
       <c r="J85" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>210141</v>
       </c>
       <c r="K85" s="2">
         <v>460000</v>
       </c>
       <c r="L85" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>182083</v>
       </c>
       <c r="M85" s="2">
@@ -6031,18 +6975,28 @@
       <c r="O85" s="2">
         <v>6</v>
       </c>
-      <c r="P85" s="2">
-        <f t="shared" si="13"/>
+      <c r="P85" s="1">
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="Q85" s="4" t="str">
-        <f>_xlfn.CONCAT(N85,"/","12/2023")</f>
-        <v>31/12/2023</v>
-      </c>
-      <c r="R85" s="4"/>
-      <c r="S85" s="4"/>
-    </row>
-    <row r="86" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q85" s="10" t="str">
+        <f t="shared" si="14"/>
+        <v>31-12-2023</v>
+      </c>
+      <c r="R85" s="2">
+        <v>0</v>
+      </c>
+      <c r="S85" s="2">
+        <v>0</v>
+      </c>
+      <c r="T85" s="2">
+        <v>0</v>
+      </c>
+      <c r="U85" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>87</v>
       </c>
@@ -6053,36 +7007,36 @@
         <v>84.3</v>
       </c>
       <c r="D86" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3096595</v>
       </c>
       <c r="E86" s="2">
         <v>126.6</v>
       </c>
       <c r="F86" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4650403</v>
       </c>
       <c r="G86" s="2">
         <v>1.49</v>
       </c>
       <c r="H86" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.49E-2</v>
       </c>
       <c r="I86" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5.9010000000000007</v>
       </c>
       <c r="J86" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>216762</v>
       </c>
       <c r="K86" s="2">
         <v>460000</v>
       </c>
       <c r="L86" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>182083</v>
       </c>
       <c r="M86" s="2">
@@ -6094,18 +7048,28 @@
       <c r="O86" s="2">
         <v>3.1</v>
       </c>
-      <c r="P86" s="2">
-        <f t="shared" si="13"/>
+      <c r="P86" s="1">
+        <f t="shared" si="15"/>
         <v>3.9</v>
       </c>
-      <c r="Q86" s="4" t="str">
-        <f>_xlfn.CONCAT(N86,"/","01/2024")</f>
-        <v>31/01/2024</v>
-      </c>
-      <c r="R86" s="4"/>
-      <c r="S86" s="4"/>
-    </row>
-    <row r="87" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q86" s="10" t="str">
+        <f t="shared" si="14"/>
+        <v>31-01-2024</v>
+      </c>
+      <c r="R86" s="2">
+        <v>0</v>
+      </c>
+      <c r="S86" s="2">
+        <v>0</v>
+      </c>
+      <c r="T86" s="2">
+        <v>0</v>
+      </c>
+      <c r="U86" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>88</v>
       </c>
@@ -6116,36 +7080,36 @@
         <v>84.3</v>
       </c>
       <c r="D87" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3107003</v>
       </c>
       <c r="E87" s="2">
         <v>126.6</v>
       </c>
       <c r="F87" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4666033</v>
       </c>
       <c r="G87" s="2">
         <v>1.49</v>
       </c>
       <c r="H87" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.49E-2</v>
       </c>
       <c r="I87" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5.9010000000000007</v>
       </c>
       <c r="J87" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>217490</v>
       </c>
       <c r="K87" s="2">
         <v>460000</v>
       </c>
       <c r="L87" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>182083</v>
       </c>
       <c r="M87" s="2">
@@ -6157,18 +7121,28 @@
       <c r="O87" s="2">
         <v>4.9000000000000004</v>
       </c>
-      <c r="P87" s="2">
-        <f t="shared" si="13"/>
+      <c r="P87" s="1">
+        <f t="shared" si="15"/>
         <v>2.0999999999999996</v>
       </c>
-      <c r="Q87" s="4" t="str">
-        <f>_xlfn.CONCAT(N87,"/","02/2024")</f>
-        <v>30/02/2024</v>
-      </c>
-      <c r="R87" s="4"/>
-      <c r="S87" s="4"/>
-    </row>
-    <row r="88" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q87" s="10" t="str">
+        <f t="shared" si="14"/>
+        <v>30-02-2024</v>
+      </c>
+      <c r="R87" s="2">
+        <v>0</v>
+      </c>
+      <c r="S87" s="2">
+        <v>0</v>
+      </c>
+      <c r="T87" s="2">
+        <v>0</v>
+      </c>
+      <c r="U87" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>89</v>
       </c>
@@ -6179,36 +7153,36 @@
         <v>84.3</v>
       </c>
       <c r="D88" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3126984</v>
       </c>
       <c r="E88" s="2">
         <v>126.6</v>
       </c>
       <c r="F88" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4696040</v>
       </c>
       <c r="G88" s="2">
         <v>1.49</v>
       </c>
       <c r="H88" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.49E-2</v>
       </c>
       <c r="I88" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5.9010000000000007</v>
       </c>
       <c r="J88" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>218889</v>
       </c>
       <c r="K88" s="2">
         <v>460000</v>
       </c>
       <c r="L88" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>182083</v>
       </c>
       <c r="M88" s="2">
@@ -6220,18 +7194,28 @@
       <c r="O88" s="2">
         <v>4.9000000000000004</v>
       </c>
-      <c r="P88" s="2">
-        <f t="shared" si="13"/>
+      <c r="P88" s="1">
+        <f t="shared" si="15"/>
         <v>2.0999999999999996</v>
       </c>
-      <c r="Q88" s="4" t="str">
-        <f>_xlfn.CONCAT(N88,"/","03/2024")</f>
-        <v>31/03/2024</v>
-      </c>
-      <c r="R88" s="4"/>
-      <c r="S88" s="4"/>
-    </row>
-    <row r="89" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q88" s="10" t="str">
+        <f t="shared" si="14"/>
+        <v>31-03-2024</v>
+      </c>
+      <c r="R88" s="2">
+        <v>0</v>
+      </c>
+      <c r="S88" s="2">
+        <v>0</v>
+      </c>
+      <c r="T88" s="2">
+        <v>0</v>
+      </c>
+      <c r="U88" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>90</v>
       </c>
@@ -6242,36 +7226,36 @@
         <v>84.3</v>
       </c>
       <c r="D89" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3141185</v>
       </c>
       <c r="E89" s="2">
         <v>126.6</v>
       </c>
       <c r="F89" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4717367</v>
       </c>
       <c r="G89" s="2">
         <v>1.49</v>
       </c>
       <c r="H89" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.49E-2</v>
       </c>
       <c r="I89" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5.9010000000000007</v>
       </c>
       <c r="J89" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>219883</v>
       </c>
       <c r="K89" s="2">
         <v>460000</v>
       </c>
       <c r="L89" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>182083</v>
       </c>
       <c r="M89" s="2">
@@ -6283,18 +7267,28 @@
       <c r="O89" s="2">
         <v>4.9000000000000004</v>
       </c>
-      <c r="P89" s="2">
-        <f t="shared" si="13"/>
+      <c r="P89" s="1">
+        <f t="shared" si="15"/>
         <v>2.0999999999999996</v>
       </c>
-      <c r="Q89" s="4" t="str">
-        <f>_xlfn.CONCAT(N89,"/","04/2024")</f>
-        <v>30/04/2024</v>
-      </c>
-      <c r="R89" s="4"/>
-      <c r="S89" s="4"/>
-    </row>
-    <row r="90" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q89" s="10" t="str">
+        <f t="shared" si="14"/>
+        <v>30-04-2024</v>
+      </c>
+      <c r="R89" s="2">
+        <v>0</v>
+      </c>
+      <c r="S89" s="2">
+        <v>0</v>
+      </c>
+      <c r="T89" s="2">
+        <v>0</v>
+      </c>
+      <c r="U89" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>91</v>
       </c>
@@ -6305,36 +7299,36 @@
         <v>84.3</v>
       </c>
       <c r="D90" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3156100</v>
       </c>
       <c r="E90" s="2">
         <v>126.6</v>
       </c>
       <c r="F90" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4739766</v>
       </c>
       <c r="G90" s="2">
         <v>1.49</v>
       </c>
       <c r="H90" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.49E-2</v>
       </c>
       <c r="I90" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5.9010000000000007</v>
       </c>
       <c r="J90" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>220927</v>
       </c>
       <c r="K90" s="2">
         <v>460000</v>
       </c>
       <c r="L90" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>182083</v>
       </c>
       <c r="M90" s="2">
@@ -6346,18 +7340,28 @@
       <c r="O90" s="2">
         <v>4.9000000000000004</v>
       </c>
-      <c r="P90" s="2">
-        <f t="shared" si="13"/>
+      <c r="P90" s="1">
+        <f t="shared" si="15"/>
         <v>2.0999999999999996</v>
       </c>
-      <c r="Q90" s="4" t="str">
-        <f>_xlfn.CONCAT(N90,"/","05/2024")</f>
-        <v>31/05/2024</v>
-      </c>
-      <c r="R90" s="4"/>
-      <c r="S90" s="4"/>
-    </row>
-    <row r="91" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q90" s="10" t="str">
+        <f t="shared" si="14"/>
+        <v>31-05-2024</v>
+      </c>
+      <c r="R90" s="2">
+        <v>0</v>
+      </c>
+      <c r="S90" s="2">
+        <v>0</v>
+      </c>
+      <c r="T90" s="2">
+        <v>0</v>
+      </c>
+      <c r="U90" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>92</v>
       </c>
@@ -6368,36 +7372,36 @@
         <v>84.3</v>
       </c>
       <c r="D91" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3167308</v>
       </c>
       <c r="E91" s="2">
         <v>126.6</v>
       </c>
       <c r="F91" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4756597</v>
       </c>
       <c r="G91" s="2">
         <v>1.49</v>
       </c>
       <c r="H91" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.49E-2</v>
       </c>
       <c r="I91" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5.9010000000000007</v>
       </c>
       <c r="J91" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>221712</v>
       </c>
       <c r="K91" s="2">
         <v>460000</v>
       </c>
       <c r="L91" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>182083</v>
       </c>
       <c r="M91" s="2">
@@ -6409,18 +7413,28 @@
       <c r="O91" s="2">
         <v>5.4</v>
       </c>
-      <c r="P91" s="2">
-        <f t="shared" si="13"/>
+      <c r="P91" s="1">
+        <f t="shared" si="15"/>
         <v>1.5999999999999996</v>
       </c>
-      <c r="Q91" s="4" t="str">
-        <f>_xlfn.CONCAT(N91,"/","06/2024")</f>
-        <v>30/06/2024</v>
-      </c>
-      <c r="R91" s="4"/>
-      <c r="S91" s="4"/>
-    </row>
-    <row r="92" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q91" s="10" t="str">
+        <f t="shared" si="14"/>
+        <v>30-06-2024</v>
+      </c>
+      <c r="R91" s="2">
+        <v>0</v>
+      </c>
+      <c r="S91" s="2">
+        <v>0</v>
+      </c>
+      <c r="T91" s="2">
+        <v>0</v>
+      </c>
+      <c r="U91" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>93</v>
       </c>
@@ -6431,36 +7445,36 @@
         <v>84.3</v>
       </c>
       <c r="D92" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3167905</v>
       </c>
       <c r="E92" s="2">
         <v>126.6</v>
       </c>
       <c r="F92" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4757495</v>
       </c>
       <c r="G92" s="2">
         <v>2.0099999999999998</v>
       </c>
       <c r="H92" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2.0099999999999996E-2</v>
       </c>
       <c r="I92" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5.9010000000000007</v>
       </c>
       <c r="J92" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>221753</v>
       </c>
       <c r="K92" s="2">
         <v>500000</v>
       </c>
       <c r="L92" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>197917</v>
       </c>
       <c r="M92" s="2">
@@ -6472,18 +7486,28 @@
       <c r="O92" s="2">
         <v>5.4</v>
       </c>
-      <c r="P92" s="2">
-        <f t="shared" si="13"/>
+      <c r="P92" s="1">
+        <f t="shared" si="15"/>
         <v>1.5999999999999996</v>
       </c>
-      <c r="Q92" s="4" t="str">
-        <f>_xlfn.CONCAT(N92,"/","07/2024")</f>
-        <v>31/07/2024</v>
-      </c>
-      <c r="R92" s="4"/>
-      <c r="S92" s="4"/>
-    </row>
-    <row r="93" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q92" s="10" t="str">
+        <f t="shared" si="14"/>
+        <v>31-07-2024</v>
+      </c>
+      <c r="R92" s="2">
+        <v>0</v>
+      </c>
+      <c r="S92" s="2">
+        <v>0</v>
+      </c>
+      <c r="T92" s="2">
+        <v>0</v>
+      </c>
+      <c r="U92" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>94</v>
       </c>
@@ -6494,36 +7518,36 @@
         <v>84.3</v>
       </c>
       <c r="D93" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3182702</v>
       </c>
       <c r="E93" s="2">
         <v>126.6</v>
       </c>
       <c r="F93" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4779716</v>
       </c>
       <c r="G93" s="2">
         <v>2.0099999999999998</v>
       </c>
       <c r="H93" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2.0099999999999996E-2</v>
       </c>
       <c r="I93" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5.9010000000000007</v>
       </c>
       <c r="J93" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>222789</v>
       </c>
       <c r="K93" s="2">
         <v>500000</v>
       </c>
       <c r="L93" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>197917</v>
       </c>
       <c r="M93" s="2">
@@ -6535,18 +7559,28 @@
       <c r="O93" s="2">
         <v>5.4</v>
       </c>
-      <c r="P93" s="2">
-        <f t="shared" si="13"/>
+      <c r="P93" s="1">
+        <f t="shared" si="15"/>
         <v>1.5999999999999996</v>
       </c>
-      <c r="Q93" s="4" t="str">
-        <f>_xlfn.CONCAT(N93,"/","08/2024")</f>
-        <v>31/08/2024</v>
-      </c>
-      <c r="R93" s="4"/>
-      <c r="S93" s="4"/>
-    </row>
-    <row r="94" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q93" s="10" t="str">
+        <f t="shared" si="14"/>
+        <v>31-08-2024</v>
+      </c>
+      <c r="R93" s="2">
+        <v>0</v>
+      </c>
+      <c r="S93" s="2">
+        <v>0</v>
+      </c>
+      <c r="T93" s="2">
+        <v>0</v>
+      </c>
+      <c r="U93" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>95</v>
       </c>
@@ -6557,36 +7591,36 @@
         <v>84.3</v>
       </c>
       <c r="D94" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3195848</v>
       </c>
       <c r="E94" s="2">
         <v>126.6</v>
       </c>
       <c r="F94" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4799459</v>
       </c>
       <c r="G94" s="2">
         <v>2.0099999999999998</v>
       </c>
       <c r="H94" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2.0099999999999996E-2</v>
       </c>
       <c r="I94" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5.9010000000000007</v>
       </c>
       <c r="J94" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>223709</v>
       </c>
       <c r="K94" s="2">
         <v>500000</v>
       </c>
       <c r="L94" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>197917</v>
       </c>
       <c r="M94" s="2">
@@ -6598,18 +7632,28 @@
       <c r="O94" s="2">
         <v>5.4</v>
       </c>
-      <c r="P94" s="2">
-        <f t="shared" si="13"/>
+      <c r="P94" s="1">
+        <f t="shared" si="15"/>
         <v>1.5999999999999996</v>
       </c>
-      <c r="Q94" s="4" t="str">
-        <f>_xlfn.CONCAT(N94,"/","09/2024")</f>
-        <v>30/09/2024</v>
-      </c>
-      <c r="R94" s="4"/>
-      <c r="S94" s="4"/>
-    </row>
-    <row r="95" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q94" s="10" t="str">
+        <f t="shared" si="14"/>
+        <v>30-09-2024</v>
+      </c>
+      <c r="R94" s="2">
+        <v>0</v>
+      </c>
+      <c r="S94" s="2">
+        <v>0</v>
+      </c>
+      <c r="T94" s="2">
+        <v>0</v>
+      </c>
+      <c r="U94" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>96</v>
       </c>
@@ -6620,36 +7664,36 @@
         <v>84.3</v>
       </c>
       <c r="D95" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3200991</v>
       </c>
       <c r="E95" s="2">
         <v>126.6</v>
       </c>
       <c r="F95" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4807182</v>
       </c>
       <c r="G95" s="2">
         <v>1.5</v>
       </c>
       <c r="H95" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="I95" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5.9010000000000007</v>
       </c>
       <c r="J95" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>224069</v>
       </c>
       <c r="K95" s="2">
         <v>500000</v>
       </c>
       <c r="L95" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>197917</v>
       </c>
       <c r="M95" s="2">
@@ -6661,18 +7705,28 @@
       <c r="O95" s="2">
         <v>5.4</v>
       </c>
-      <c r="P95" s="2">
-        <f t="shared" si="13"/>
+      <c r="P95" s="1">
+        <f t="shared" si="15"/>
         <v>1.5999999999999996</v>
       </c>
-      <c r="Q95" s="4" t="str">
-        <f>_xlfn.CONCAT(N95,"/","10/2024")</f>
-        <v>31/10/2024</v>
-      </c>
-      <c r="R95" s="4"/>
-      <c r="S95" s="4"/>
-    </row>
-    <row r="96" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q95" s="10" t="str">
+        <f t="shared" si="14"/>
+        <v>31-10-2024</v>
+      </c>
+      <c r="R95" s="2">
+        <v>0</v>
+      </c>
+      <c r="S95" s="2">
+        <v>0</v>
+      </c>
+      <c r="T95" s="2">
+        <v>0</v>
+      </c>
+      <c r="U95" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>97</v>
       </c>
@@ -6683,36 +7737,36 @@
         <v>84.3</v>
       </c>
       <c r="D96" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3224300</v>
       </c>
       <c r="E96" s="2">
         <v>126.6</v>
       </c>
       <c r="F96" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4842187</v>
       </c>
       <c r="G96" s="2">
         <v>1.5</v>
       </c>
       <c r="H96" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="I96" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5.9010000000000007</v>
       </c>
       <c r="J96" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>225701</v>
       </c>
       <c r="K96" s="2">
         <v>500000</v>
       </c>
       <c r="L96" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>197917</v>
       </c>
       <c r="M96" s="2">
@@ -6724,18 +7778,28 @@
       <c r="O96" s="2">
         <v>5.4</v>
       </c>
-      <c r="P96" s="2">
-        <f t="shared" si="13"/>
+      <c r="P96" s="1">
+        <f t="shared" si="15"/>
         <v>1.5999999999999996</v>
       </c>
-      <c r="Q96" s="4" t="str">
-        <f>_xlfn.CONCAT(N96,"/","11/2024")</f>
-        <v>30/11/2024</v>
-      </c>
-      <c r="R96" s="4"/>
-      <c r="S96" s="4"/>
-    </row>
-    <row r="97" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q96" s="10" t="str">
+        <f t="shared" si="14"/>
+        <v>30-11-2024</v>
+      </c>
+      <c r="R96" s="2">
+        <v>0</v>
+      </c>
+      <c r="S96" s="2">
+        <v>0</v>
+      </c>
+      <c r="T96" s="2">
+        <v>0</v>
+      </c>
+      <c r="U96" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>98</v>
       </c>
@@ -6746,36 +7810,36 @@
         <v>84.3</v>
       </c>
       <c r="D97" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3238527</v>
       </c>
       <c r="E97" s="2">
         <v>126.6</v>
       </c>
       <c r="F97" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4863553</v>
       </c>
       <c r="G97" s="2">
         <v>1.5</v>
       </c>
       <c r="H97" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="I97" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5.9010000000000007</v>
       </c>
       <c r="J97" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>226697</v>
       </c>
       <c r="K97" s="2">
         <v>500000</v>
       </c>
       <c r="L97" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>197917</v>
       </c>
       <c r="M97" s="2">
@@ -6787,18 +7851,28 @@
       <c r="O97" s="2">
         <v>5.4</v>
       </c>
-      <c r="P97" s="2">
-        <f t="shared" si="13"/>
+      <c r="P97" s="1">
+        <f t="shared" si="15"/>
         <v>1.5999999999999996</v>
       </c>
-      <c r="Q97" s="4" t="str">
-        <f>_xlfn.CONCAT(N97,"/","12/2024")</f>
-        <v>31/12/2024</v>
-      </c>
-      <c r="R97" s="4"/>
-      <c r="S97" s="4"/>
-    </row>
-    <row r="98" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q97" s="10" t="str">
+        <f t="shared" si="14"/>
+        <v>31-12-2024</v>
+      </c>
+      <c r="R97" s="2">
+        <v>0</v>
+      </c>
+      <c r="S97" s="2">
+        <v>0</v>
+      </c>
+      <c r="T97" s="2">
+        <v>0</v>
+      </c>
+      <c r="U97" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>99</v>
       </c>
@@ -6809,36 +7883,36 @@
         <v>87.8</v>
       </c>
       <c r="D98" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3370151</v>
       </c>
       <c r="E98" s="2">
         <v>131.80000000000001</v>
       </c>
       <c r="F98" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>5059065</v>
       </c>
       <c r="G98" s="2">
         <v>1.38</v>
       </c>
       <c r="H98" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.38E-2</v>
       </c>
       <c r="I98" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>6.1460000000000008</v>
       </c>
       <c r="J98" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>235911</v>
       </c>
       <c r="K98" s="2">
         <v>510636</v>
       </c>
       <c r="L98" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>202127</v>
       </c>
       <c r="M98" s="6">
@@ -6850,17 +7924,27 @@
       <c r="O98" s="2">
         <v>3.1</v>
       </c>
-      <c r="P98" s="2">
-        <f t="shared" si="13"/>
+      <c r="P98" s="1">
+        <f t="shared" si="15"/>
         <v>3.9</v>
       </c>
       <c r="Q98" s="4">
         <v>45688</v>
       </c>
-      <c r="R98" s="4"/>
-      <c r="S98" s="4"/>
-    </row>
-    <row r="99" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R98" s="2">
+        <v>0</v>
+      </c>
+      <c r="S98" s="2">
+        <v>0</v>
+      </c>
+      <c r="T98" s="2">
+        <v>0</v>
+      </c>
+      <c r="U98" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>100</v>
       </c>
@@ -6871,36 +7955,36 @@
         <v>87.8</v>
       </c>
       <c r="D99" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3393289</v>
       </c>
       <c r="E99" s="2">
         <v>131.9</v>
       </c>
       <c r="F99" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>5097663</v>
       </c>
       <c r="G99" s="2">
         <v>1.38</v>
       </c>
       <c r="H99" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.38E-2</v>
       </c>
       <c r="I99" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>6.1460000000000008</v>
       </c>
       <c r="J99" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>237530</v>
       </c>
       <c r="K99" s="2">
         <v>510636</v>
       </c>
       <c r="L99" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>202127</v>
       </c>
       <c r="M99" s="6">
@@ -6912,17 +7996,27 @@
       <c r="O99" s="2">
         <v>5.2</v>
       </c>
-      <c r="P99" s="2">
-        <f t="shared" si="13"/>
+      <c r="P99" s="1">
+        <f t="shared" si="15"/>
         <v>1.7999999999999998</v>
       </c>
       <c r="Q99" s="4">
         <v>45716</v>
       </c>
-      <c r="R99" s="2"/>
-      <c r="S99" s="2"/>
-    </row>
-    <row r="100" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R99" s="2">
+        <v>0</v>
+      </c>
+      <c r="S99" s="2">
+        <v>0</v>
+      </c>
+      <c r="T99" s="2">
+        <v>0</v>
+      </c>
+      <c r="U99" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>101</v>
       </c>
@@ -6933,36 +8027,36 @@
         <v>87.8</v>
       </c>
       <c r="D100" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3414903</v>
       </c>
       <c r="E100" s="2">
         <v>131.9</v>
       </c>
       <c r="F100" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>5130133</v>
       </c>
       <c r="G100" s="2">
         <v>1.38</v>
       </c>
       <c r="H100" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.38E-2</v>
       </c>
       <c r="I100" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>6.1460000000000008</v>
       </c>
       <c r="J100" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>239043</v>
       </c>
       <c r="K100" s="2">
         <v>510636</v>
       </c>
       <c r="L100" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>202127</v>
       </c>
       <c r="M100" s="6">
@@ -6974,17 +8068,27 @@
       <c r="O100" s="2">
         <v>5.2</v>
       </c>
-      <c r="P100" s="2">
-        <f t="shared" si="13"/>
+      <c r="P100" s="1">
+        <f t="shared" si="15"/>
         <v>1.7999999999999998</v>
       </c>
       <c r="Q100" s="4">
         <v>45747</v>
       </c>
-      <c r="R100" s="2"/>
-      <c r="S100" s="2"/>
-    </row>
-    <row r="101" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R100" s="2">
+        <v>0</v>
+      </c>
+      <c r="S100" s="2">
+        <v>0</v>
+      </c>
+      <c r="T100" s="2">
+        <v>0</v>
+      </c>
+      <c r="U100" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>102</v>
       </c>
@@ -6995,36 +8099,36 @@
         <v>87.8</v>
       </c>
       <c r="D101" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3430821</v>
       </c>
       <c r="E101" s="2">
         <v>131.9</v>
       </c>
       <c r="F101" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>5154047</v>
       </c>
       <c r="G101" s="2">
         <v>1.78</v>
       </c>
       <c r="H101" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.78E-2</v>
       </c>
       <c r="I101" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>6.1460000000000008</v>
       </c>
       <c r="J101" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>240157</v>
       </c>
       <c r="K101" s="2">
         <v>510636</v>
       </c>
       <c r="L101" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>202127</v>
       </c>
       <c r="M101" s="6">
@@ -7036,17 +8140,27 @@
       <c r="O101" s="2">
         <v>5.2</v>
       </c>
-      <c r="P101" s="2">
-        <f t="shared" si="13"/>
+      <c r="P101" s="1">
+        <f t="shared" si="15"/>
         <v>1.7999999999999998</v>
       </c>
       <c r="Q101" s="4">
         <v>45777</v>
       </c>
-      <c r="R101" s="4"/>
-      <c r="S101" s="4"/>
-    </row>
-    <row r="102" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R101" s="2">
+        <v>0</v>
+      </c>
+      <c r="S101" s="2">
+        <v>0</v>
+      </c>
+      <c r="T101" s="2">
+        <v>0</v>
+      </c>
+      <c r="U101" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>103</v>
       </c>
@@ -7057,36 +8171,36 @@
         <v>87.8</v>
       </c>
       <c r="D102" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3440834</v>
       </c>
       <c r="E102" s="2">
         <v>131.9</v>
       </c>
       <c r="F102" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>5169088</v>
       </c>
       <c r="G102" s="2">
         <v>1.78</v>
       </c>
       <c r="H102" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.78E-2</v>
       </c>
       <c r="I102" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>6.1460000000000008</v>
       </c>
       <c r="J102" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>240858</v>
       </c>
       <c r="K102" s="2">
         <v>529000</v>
       </c>
       <c r="L102" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>209396</v>
       </c>
       <c r="M102" s="6">
@@ -7098,17 +8212,27 @@
       <c r="O102" s="2">
         <v>5.2</v>
       </c>
-      <c r="P102" s="2">
-        <f t="shared" si="13"/>
+      <c r="P102" s="1">
+        <f t="shared" si="15"/>
         <v>1.7999999999999998</v>
       </c>
       <c r="Q102" s="4">
         <v>45808</v>
       </c>
-      <c r="R102" s="4"/>
-      <c r="S102" s="4"/>
-    </row>
-    <row r="103" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R102" s="2">
+        <v>0</v>
+      </c>
+      <c r="S102" s="2">
+        <v>0</v>
+      </c>
+      <c r="T102" s="2">
+        <v>0</v>
+      </c>
+      <c r="U102" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>104</v>
       </c>
@@ -7119,36 +8243,36 @@
         <v>87.8</v>
       </c>
       <c r="D103" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3447649</v>
       </c>
       <c r="E103" s="2">
         <v>131.9</v>
       </c>
       <c r="F103" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>5179327</v>
       </c>
       <c r="G103" s="2">
         <v>1.78</v>
       </c>
       <c r="H103" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.78E-2</v>
       </c>
       <c r="I103" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>6.1460000000000008</v>
       </c>
       <c r="J103" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>241335</v>
       </c>
       <c r="K103" s="2">
         <v>529000</v>
       </c>
       <c r="L103" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>209396</v>
       </c>
       <c r="M103" s="6">
@@ -7160,17 +8284,27 @@
       <c r="O103" s="2">
         <v>5.2</v>
       </c>
-      <c r="P103" s="2">
-        <f t="shared" si="13"/>
+      <c r="P103" s="1">
+        <f t="shared" si="15"/>
         <v>1.7999999999999998</v>
       </c>
       <c r="Q103" s="4">
         <v>45838</v>
       </c>
-      <c r="R103" s="4"/>
-      <c r="S103" s="4"/>
-    </row>
-    <row r="104" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R103" s="2">
+        <v>0</v>
+      </c>
+      <c r="S103" s="2">
+        <v>0</v>
+      </c>
+      <c r="T103" s="2">
+        <v>0</v>
+      </c>
+      <c r="U103" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>105</v>
       </c>
@@ -7181,36 +8315,36 @@
         <v>87.8</v>
       </c>
       <c r="D104" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3439917</v>
       </c>
       <c r="E104" s="2">
         <v>131.9</v>
       </c>
       <c r="F104" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>5167711</v>
       </c>
       <c r="G104" s="2">
         <v>1.88</v>
       </c>
       <c r="H104" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.8799999999999997E-2</v>
       </c>
       <c r="I104" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>6.1460000000000008</v>
       </c>
       <c r="J104" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>240794</v>
       </c>
       <c r="K104" s="2">
         <v>529000</v>
       </c>
       <c r="L104" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>209396</v>
       </c>
       <c r="M104" s="6">
@@ -7222,17 +8356,27 @@
       <c r="O104" s="2">
         <v>5.2</v>
       </c>
-      <c r="P104" s="2">
-        <f t="shared" si="13"/>
+      <c r="P104" s="1">
+        <f t="shared" si="15"/>
         <v>1.7999999999999998</v>
       </c>
       <c r="Q104" s="4">
         <v>45869</v>
       </c>
-      <c r="R104" s="4"/>
-      <c r="S104" s="4"/>
-    </row>
-    <row r="105" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R104" s="2">
+        <v>0</v>
+      </c>
+      <c r="S104" s="2">
+        <v>0</v>
+      </c>
+      <c r="T104" s="2">
+        <v>0</v>
+      </c>
+      <c r="U104" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>106</v>
       </c>
@@ -7243,36 +8387,36 @@
         <v>87.8</v>
       </c>
       <c r="D105" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3457834</v>
       </c>
       <c r="E105" s="2">
         <v>131.9</v>
       </c>
       <c r="F105" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>5194627</v>
       </c>
       <c r="G105" s="2">
         <v>1.88</v>
       </c>
       <c r="H105" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.8799999999999997E-2</v>
       </c>
       <c r="I105" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>6.1460000000000008</v>
       </c>
       <c r="J105" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>242048</v>
       </c>
       <c r="K105" s="2">
         <v>529000</v>
       </c>
       <c r="L105" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>209396</v>
       </c>
       <c r="M105" s="6">
@@ -7284,8 +8428,8 @@
       <c r="O105" s="2">
         <v>5.2</v>
       </c>
-      <c r="P105" s="2">
-        <f t="shared" si="13"/>
+      <c r="P105" s="1">
+        <f t="shared" si="15"/>
         <v>1.7999999999999998</v>
       </c>
       <c r="Q105" s="4">
@@ -7297,8 +8441,14 @@
       <c r="S105" s="2">
         <v>0.9</v>
       </c>
-    </row>
-    <row r="106" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T105" s="2">
+        <v>0</v>
+      </c>
+      <c r="U105" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>107</v>
       </c>
@@ -7309,36 +8459,36 @@
         <v>87.8</v>
       </c>
       <c r="D106" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3466840</v>
       </c>
       <c r="E106" s="2">
         <v>131.9</v>
       </c>
       <c r="F106" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>5208157</v>
       </c>
       <c r="G106" s="2">
         <v>1.88</v>
       </c>
       <c r="H106" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.8799999999999997E-2</v>
       </c>
       <c r="I106" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>6.1460000000000008</v>
       </c>
       <c r="J106" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>242679</v>
       </c>
       <c r="K106" s="2">
         <v>529000</v>
       </c>
       <c r="L106" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>209396</v>
       </c>
       <c r="M106" s="6">
@@ -7350,8 +8500,8 @@
       <c r="O106" s="2">
         <v>5.2</v>
       </c>
-      <c r="P106" s="2">
-        <f t="shared" si="13"/>
+      <c r="P106" s="1">
+        <f t="shared" si="15"/>
         <v>1.7999999999999998</v>
       </c>
       <c r="Q106" s="4">
@@ -7363,8 +8513,14 @@
       <c r="S106" s="2">
         <v>0.9</v>
       </c>
-    </row>
-    <row r="107" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T106" s="2">
+        <v>0</v>
+      </c>
+      <c r="U106" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>108</v>
       </c>
@@ -7375,36 +8531,36 @@
         <v>87.8</v>
       </c>
       <c r="D107" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3476675</v>
       </c>
       <c r="E107" s="2">
         <v>131.9</v>
       </c>
       <c r="F107" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>5222933</v>
       </c>
       <c r="G107" s="2">
         <v>1.49</v>
       </c>
       <c r="H107" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.49E-2</v>
       </c>
       <c r="I107" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>6.1460000000000008</v>
       </c>
       <c r="J107" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>243367</v>
       </c>
       <c r="K107" s="2">
         <v>529000</v>
       </c>
       <c r="L107" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>209396</v>
       </c>
       <c r="M107" s="6">
@@ -7416,8 +8572,8 @@
       <c r="O107" s="2">
         <v>5.2</v>
       </c>
-      <c r="P107" s="2">
-        <f t="shared" si="13"/>
+      <c r="P107" s="1">
+        <f t="shared" si="15"/>
         <v>1.7999999999999998</v>
       </c>
       <c r="Q107" s="4">
@@ -7429,8 +8585,14 @@
       <c r="S107" s="2">
         <v>0.9</v>
       </c>
-    </row>
-    <row r="108" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T107" s="2">
+        <v>0</v>
+      </c>
+      <c r="U107" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>109</v>
       </c>
@@ -7441,36 +8603,36 @@
         <v>87.8</v>
       </c>
       <c r="D108" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3480707</v>
       </c>
       <c r="E108" s="2">
         <v>131.9</v>
       </c>
       <c r="F108" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>5228990</v>
       </c>
       <c r="G108" s="2">
         <v>1.49</v>
       </c>
       <c r="H108" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.49E-2</v>
       </c>
       <c r="I108" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>6.1460000000000008</v>
       </c>
       <c r="J108" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>243650</v>
       </c>
       <c r="K108" s="2">
         <v>529000</v>
       </c>
       <c r="L108" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>209396</v>
       </c>
       <c r="M108" s="6">
@@ -7482,8 +8644,8 @@
       <c r="O108" s="2">
         <v>4.5</v>
       </c>
-      <c r="P108" s="2">
-        <f t="shared" si="13"/>
+      <c r="P108" s="1">
+        <f t="shared" si="15"/>
         <v>2.5</v>
       </c>
       <c r="Q108" s="4">
@@ -7495,8 +8657,14 @@
       <c r="S108" s="2">
         <v>0.9</v>
       </c>
-    </row>
-    <row r="109" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T108" s="2">
+        <v>0</v>
+      </c>
+      <c r="U108" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>110</v>
       </c>
@@ -7507,36 +8675,36 @@
         <v>87.8</v>
       </c>
       <c r="D109" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3488115</v>
       </c>
       <c r="E109" s="2">
         <v>131.9</v>
       </c>
       <c r="F109" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>5240118</v>
       </c>
       <c r="G109" s="2">
         <v>1.49</v>
       </c>
       <c r="H109" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.49E-2</v>
       </c>
       <c r="I109" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>6.1460000000000008</v>
       </c>
       <c r="J109" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>244168</v>
       </c>
       <c r="K109" s="2">
         <v>529000</v>
       </c>
       <c r="L109" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>209396</v>
       </c>
       <c r="M109" s="6">
@@ -7548,8 +8716,8 @@
       <c r="O109" s="2">
         <v>4.5</v>
       </c>
-      <c r="P109" s="2">
-        <f t="shared" si="13"/>
+      <c r="P109" s="1">
+        <f t="shared" si="15"/>
         <v>2.5</v>
       </c>
       <c r="Q109" s="4">
@@ -7561,8 +8729,14 @@
       <c r="S109" s="2">
         <v>0.9</v>
       </c>
-    </row>
-    <row r="110" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T109" s="2">
+        <v>0</v>
+      </c>
+      <c r="U109" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>111</v>
       </c>
@@ -7573,36 +8747,36 @@
         <v>89.9</v>
       </c>
       <c r="D110" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3569576</v>
       </c>
       <c r="E110" s="2">
         <v>135.1</v>
       </c>
       <c r="F110" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>5364290</v>
       </c>
       <c r="G110" s="2">
         <v>1.54</v>
       </c>
       <c r="H110" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.54E-2</v>
       </c>
       <c r="I110" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>6.293000000000001</v>
       </c>
       <c r="J110" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>249870</v>
       </c>
       <c r="K110" s="2">
         <v>539000</v>
       </c>
       <c r="L110" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>213354</v>
       </c>
       <c r="M110" s="6">
@@ -7614,8 +8788,8 @@
       <c r="O110" s="2">
         <v>3.1</v>
       </c>
-      <c r="P110" s="2">
-        <f t="shared" si="13"/>
+      <c r="P110" s="1">
+        <f t="shared" si="15"/>
         <v>3.9</v>
       </c>
       <c r="Q110" s="4">
@@ -7627,8 +8801,14 @@
       <c r="S110" s="2">
         <v>0.9</v>
       </c>
-    </row>
-    <row r="111" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T110" s="2">
+        <v>0</v>
+      </c>
+      <c r="U110" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>112</v>
       </c>
@@ -7639,36 +8819,36 @@
         <v>90</v>
       </c>
       <c r="D111" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3581157</v>
       </c>
       <c r="E111" s="2">
         <v>135.19999999999999</v>
       </c>
       <c r="F111" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>5379693</v>
       </c>
       <c r="G111" s="2">
         <v>1.54</v>
       </c>
       <c r="H111" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.54E-2</v>
       </c>
       <c r="I111" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>6.3000000000000007</v>
       </c>
       <c r="J111" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>250681</v>
       </c>
       <c r="K111" s="2">
         <v>539000</v>
       </c>
       <c r="L111" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>213354</v>
       </c>
       <c r="M111" s="6">
@@ -7680,8 +8860,8 @@
       <c r="O111" s="2">
         <v>4.2</v>
       </c>
-      <c r="P111" s="2">
-        <f t="shared" si="13"/>
+      <c r="P111" s="1">
+        <f t="shared" si="15"/>
         <v>2.8</v>
       </c>
       <c r="Q111" s="4">
@@ -7693,8 +8873,14 @@
       <c r="S111" s="2">
         <v>0.9</v>
       </c>
-    </row>
-    <row r="112" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T111" s="2">
+        <v>0</v>
+      </c>
+      <c r="U111" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>113</v>
       </c>
@@ -7705,36 +8891,36 @@
         <v>90</v>
       </c>
       <c r="D112" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3585755</v>
       </c>
       <c r="E112" s="2">
         <v>135.19999999999999</v>
       </c>
       <c r="F112" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>5386601</v>
       </c>
       <c r="G112" s="2">
         <v>1.54</v>
       </c>
       <c r="H112" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.54E-2</v>
       </c>
       <c r="I112" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>6.3000000000000007</v>
       </c>
       <c r="J112" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>251003</v>
       </c>
       <c r="K112" s="2">
         <v>539000</v>
       </c>
       <c r="L112" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>213354</v>
       </c>
       <c r="M112" s="6">
@@ -7746,8 +8932,8 @@
       <c r="O112" s="2">
         <v>4.2</v>
       </c>
-      <c r="P112" s="2">
-        <f t="shared" si="13"/>
+      <c r="P112" s="1">
+        <f t="shared" si="15"/>
         <v>2.8</v>
       </c>
       <c r="Q112" s="4">
@@ -7759,8 +8945,14 @@
       <c r="S112" s="2">
         <v>0.9</v>
       </c>
-    </row>
-    <row r="113" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T112" s="2">
+        <v>0</v>
+      </c>
+      <c r="U112" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>114</v>
       </c>
@@ -7771,36 +8963,36 @@
         <v>90</v>
       </c>
       <c r="D113" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3610818</v>
       </c>
       <c r="E113" s="2">
         <v>135.19999999999999</v>
       </c>
       <c r="F113" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>5424251</v>
       </c>
       <c r="G113" s="2">
         <v>1.62</v>
       </c>
       <c r="H113" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.6200000000000003E-2</v>
       </c>
       <c r="I113" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>6.3000000000000007</v>
       </c>
       <c r="J113" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>252757</v>
       </c>
       <c r="K113" s="2">
         <v>539000</v>
       </c>
       <c r="L113" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>213354</v>
       </c>
       <c r="M113" s="6">
@@ -7812,8 +9004,8 @@
       <c r="O113" s="2">
         <v>4.2</v>
       </c>
-      <c r="P113" s="2">
-        <f t="shared" si="13"/>
+      <c r="P113" s="1">
+        <f t="shared" si="15"/>
         <v>2.8</v>
       </c>
       <c r="Q113" s="4">
@@ -7825,198 +9017,1668 @@
       <c r="S113" s="2">
         <v>0.9</v>
       </c>
+      <c r="T113" s="2">
+        <v>0</v>
+      </c>
+      <c r="U113" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A114" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B114" s="2">
+        <v>40610.69</v>
+      </c>
+      <c r="C114" s="2">
+        <v>90</v>
+      </c>
+      <c r="D114" s="1">
+        <f t="shared" si="8"/>
+        <v>3654962</v>
+      </c>
+      <c r="E114" s="2">
+        <v>135.19999999999999</v>
+      </c>
+      <c r="F114" s="1">
+        <f t="shared" si="9"/>
+        <v>5490565</v>
+      </c>
+      <c r="G114" s="2">
+        <v>1.62</v>
+      </c>
+      <c r="H114" s="1">
+        <f t="shared" ref="H114:H121" si="16">G114/100</f>
+        <v>1.6200000000000003E-2</v>
+      </c>
+      <c r="I114" s="1">
+        <f t="shared" ref="I114:I121" si="17">+C114*0.07</f>
+        <v>6.3000000000000007</v>
+      </c>
+      <c r="J114" s="1">
+        <f t="shared" ref="J114:J121" si="18">ROUND(B114*I114,0)</f>
+        <v>255847</v>
+      </c>
+      <c r="K114" s="2">
+        <v>539000</v>
+      </c>
+      <c r="L114" s="3">
+        <f t="shared" si="13"/>
+        <v>213354</v>
+      </c>
+      <c r="M114" s="7">
+        <v>70588</v>
+      </c>
+      <c r="N114" s="2">
+        <v>31</v>
+      </c>
+      <c r="O114" s="2">
+        <v>4.2</v>
+      </c>
+      <c r="P114" s="1">
+        <f t="shared" si="15"/>
+        <v>2.8</v>
+      </c>
+      <c r="Q114" s="4">
+        <v>46173</v>
+      </c>
+      <c r="R114" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="S114" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="T114" s="2">
+        <v>0</v>
+      </c>
+      <c r="U114" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A115" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B115" s="2">
+        <v>40820.31</v>
+      </c>
+      <c r="C115" s="2">
+        <v>90</v>
+      </c>
+      <c r="D115" s="1">
+        <f t="shared" si="8"/>
+        <v>3673828</v>
+      </c>
+      <c r="E115" s="2">
+        <v>135.19999999999999</v>
+      </c>
+      <c r="F115" s="1">
+        <f t="shared" si="9"/>
+        <v>5518906</v>
+      </c>
+      <c r="G115" s="2">
+        <v>1.62</v>
+      </c>
+      <c r="H115" s="1">
+        <f t="shared" si="16"/>
+        <v>1.6200000000000003E-2</v>
+      </c>
+      <c r="I115" s="1">
+        <f t="shared" si="17"/>
+        <v>6.3000000000000007</v>
+      </c>
+      <c r="J115" s="1">
+        <f t="shared" si="18"/>
+        <v>257168</v>
+      </c>
+      <c r="K115" s="2">
+        <v>553553</v>
+      </c>
+      <c r="L115" s="3">
+        <f t="shared" si="13"/>
+        <v>219115</v>
+      </c>
+      <c r="M115" s="7">
+        <v>71506</v>
+      </c>
+      <c r="N115" s="2">
+        <v>30</v>
+      </c>
+      <c r="O115" s="2">
+        <v>4.2</v>
+      </c>
+      <c r="P115" s="1">
+        <f t="shared" si="15"/>
+        <v>2.8</v>
+      </c>
+      <c r="Q115" s="4">
+        <v>46203</v>
+      </c>
+      <c r="R115" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="S115" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="T115" s="2">
+        <v>0</v>
+      </c>
+      <c r="U115" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A116" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B116" s="2">
+        <v>40844.79</v>
+      </c>
+      <c r="C116" s="2">
+        <v>90</v>
+      </c>
+      <c r="D116" s="1">
+        <f t="shared" si="8"/>
+        <v>3676031</v>
+      </c>
+      <c r="E116" s="2">
+        <v>135.19999999999999</v>
+      </c>
+      <c r="F116" s="1">
+        <f t="shared" si="9"/>
+        <v>5522216</v>
+      </c>
+      <c r="G116" s="8">
+        <v>2</v>
+      </c>
+      <c r="H116" s="1">
+        <f t="shared" si="16"/>
+        <v>0.02</v>
+      </c>
+      <c r="I116" s="1">
+        <f t="shared" si="17"/>
+        <v>6.3000000000000007</v>
+      </c>
+      <c r="J116" s="1">
+        <f t="shared" si="18"/>
+        <v>257322</v>
+      </c>
+      <c r="K116" s="2">
+        <v>553553</v>
+      </c>
+      <c r="L116" s="3">
+        <f t="shared" si="13"/>
+        <v>219115</v>
+      </c>
+      <c r="M116" s="9">
+        <v>71649</v>
+      </c>
+      <c r="N116" s="2">
+        <v>31</v>
+      </c>
+      <c r="O116" s="2">
+        <v>4.2</v>
+      </c>
+      <c r="P116" s="1">
+        <f t="shared" si="15"/>
+        <v>2.8</v>
+      </c>
+      <c r="Q116" s="4">
+        <v>46234</v>
+      </c>
+      <c r="R116" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="S116" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="T116" s="2">
+        <v>0</v>
+      </c>
+      <c r="U116" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A117" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B117" s="16">
+        <v>40873.769999999997</v>
+      </c>
+      <c r="C117" s="2">
+        <v>90</v>
+      </c>
+      <c r="D117" s="1">
+        <f t="shared" si="8"/>
+        <v>3678639</v>
+      </c>
+      <c r="E117" s="2">
+        <v>135.19999999999999</v>
+      </c>
+      <c r="F117" s="1">
+        <f t="shared" si="9"/>
+        <v>5526134</v>
+      </c>
+      <c r="G117" s="2">
+        <v>1.78</v>
+      </c>
+      <c r="H117" s="1">
+        <f t="shared" si="16"/>
+        <v>1.78E-2</v>
+      </c>
+      <c r="I117" s="1">
+        <f t="shared" si="17"/>
+        <v>6.3000000000000007</v>
+      </c>
+      <c r="J117" s="1">
+        <f t="shared" si="18"/>
+        <v>257505</v>
+      </c>
+      <c r="K117" s="2">
+        <v>553553</v>
+      </c>
+      <c r="L117" s="3">
+        <f t="shared" si="13"/>
+        <v>219115</v>
+      </c>
+      <c r="M117" s="2">
+        <v>72649</v>
+      </c>
+      <c r="N117" s="2">
+        <v>31</v>
+      </c>
+      <c r="O117" s="2">
+        <v>4.2</v>
+      </c>
+      <c r="P117" s="1">
+        <f t="shared" si="15"/>
+        <v>2.8</v>
+      </c>
+      <c r="Q117" s="4">
+        <v>46265</v>
+      </c>
+      <c r="R117" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="S117" s="2">
+        <v>0.72</v>
+      </c>
+      <c r="T117" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="U117" s="2">
+        <f>+S117+G117</f>
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="118" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A118" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B118" s="2"/>
+      <c r="C118" s="2"/>
+      <c r="D118" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="E118" s="2"/>
+      <c r="F118" s="1">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G118" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="H118" s="1">
+        <f t="shared" si="16"/>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="I118" s="1">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="J118" s="1">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="K118" s="2"/>
+      <c r="L118" s="3">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="M118" s="2"/>
+      <c r="N118" s="2">
+        <v>30</v>
+      </c>
+      <c r="O118" s="2"/>
+      <c r="P118" s="1">
+        <f t="shared" si="15"/>
+        <v>7</v>
+      </c>
+      <c r="Q118" s="4">
+        <v>46295</v>
+      </c>
+      <c r="R118" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="S118" s="2"/>
+      <c r="T118" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="U118" s="2">
+        <f t="shared" ref="U118:U140" si="19">+S118+G118</f>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="119" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A119" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B119" s="2"/>
+      <c r="C119" s="2"/>
+      <c r="D119" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="E119" s="2"/>
+      <c r="F119" s="1">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G119" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="H119" s="1">
+        <f t="shared" si="16"/>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="I119" s="1">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="J119" s="1">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="K119" s="2"/>
+      <c r="L119" s="3">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="M119" s="2"/>
+      <c r="N119" s="2">
+        <v>31</v>
+      </c>
+      <c r="O119" s="2"/>
+      <c r="P119" s="1">
+        <f t="shared" si="15"/>
+        <v>7</v>
+      </c>
+      <c r="Q119" s="4">
+        <v>46326</v>
+      </c>
+      <c r="R119" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="S119" s="2"/>
+      <c r="T119" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="U119" s="2">
+        <f t="shared" si="19"/>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="120" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A120" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B120" s="2"/>
+      <c r="C120" s="2"/>
+      <c r="D120" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="E120" s="2"/>
+      <c r="F120" s="1">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G120" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="H120" s="1">
+        <f t="shared" si="16"/>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="I120" s="1">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="J120" s="1">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="K120" s="2"/>
+      <c r="L120" s="3">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="M120" s="2"/>
+      <c r="N120" s="2">
+        <v>30</v>
+      </c>
+      <c r="O120" s="2"/>
+      <c r="P120" s="1">
+        <f t="shared" si="15"/>
+        <v>7</v>
+      </c>
+      <c r="Q120" s="4">
+        <v>46356</v>
+      </c>
+      <c r="R120" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="S120" s="2"/>
+      <c r="T120" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="U120" s="2">
+        <f t="shared" si="19"/>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="121" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A121" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B121" s="2"/>
+      <c r="C121" s="2"/>
+      <c r="D121" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="E121" s="2"/>
+      <c r="F121" s="1">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G121" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="H121" s="1">
+        <f t="shared" si="16"/>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="I121" s="1">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="J121" s="1">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="K121" s="2"/>
+      <c r="L121" s="3">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="M121" s="2"/>
+      <c r="N121" s="2">
+        <v>31</v>
+      </c>
+      <c r="O121" s="2"/>
+      <c r="P121" s="1">
+        <f t="shared" si="15"/>
+        <v>7</v>
+      </c>
+      <c r="Q121" s="4">
+        <v>46387</v>
+      </c>
+      <c r="R121" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="S121" s="2"/>
+      <c r="T121" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="U121" s="2">
+        <f t="shared" si="19"/>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="122" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A122" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B122" s="2"/>
+      <c r="C122" s="2"/>
+      <c r="D122" s="1">
+        <f t="shared" ref="D122:D133" si="20">ROUND(B122*C122,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E122" s="2"/>
+      <c r="F122" s="1">
+        <f t="shared" ref="F122:F133" si="21">ROUND(B122*E122,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G122" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="H122" s="1">
+        <f t="shared" ref="H122:H133" si="22">G122/100</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="I122" s="1">
+        <f t="shared" ref="I122:I133" si="23">+C122*0.07</f>
+        <v>0</v>
+      </c>
+      <c r="J122" s="1">
+        <f t="shared" ref="J122:J133" si="24">ROUND(B122*I122,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K122" s="2"/>
+      <c r="L122" s="3">
+        <f t="shared" ref="L122:L140" si="25">ROUND((K122*4.75)/12,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M122" s="2"/>
+      <c r="N122" s="2">
+        <v>31</v>
+      </c>
+      <c r="O122" s="2"/>
+      <c r="P122" s="1">
+        <f t="shared" si="15"/>
+        <v>7</v>
+      </c>
+      <c r="Q122" s="4">
+        <v>46418</v>
+      </c>
+      <c r="R122" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="S122" s="2"/>
+      <c r="T122" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="U122" s="2">
+        <f t="shared" si="19"/>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="123" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A123" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B123" s="2"/>
+      <c r="C123" s="2"/>
+      <c r="D123" s="1">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="E123" s="2"/>
+      <c r="F123" s="1">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="G123" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="H123" s="1">
+        <f t="shared" si="22"/>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="I123" s="1">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="J123" s="1">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="K123" s="2"/>
+      <c r="L123" s="3">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="M123" s="2"/>
+      <c r="N123" s="2">
+        <v>30</v>
+      </c>
+      <c r="O123" s="2"/>
+      <c r="P123" s="1">
+        <f t="shared" si="15"/>
+        <v>7</v>
+      </c>
+      <c r="Q123" s="4">
+        <v>46446</v>
+      </c>
+      <c r="R123" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="S123" s="2"/>
+      <c r="T123" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="U123" s="2">
+        <f t="shared" si="19"/>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="124" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A124" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B124" s="2"/>
+      <c r="C124" s="2"/>
+      <c r="D124" s="1">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="E124" s="2"/>
+      <c r="F124" s="1">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="G124" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="H124" s="1">
+        <f t="shared" si="22"/>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="I124" s="1">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="J124" s="1">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="K124" s="2"/>
+      <c r="L124" s="3">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="M124" s="2"/>
+      <c r="N124" s="2">
+        <v>31</v>
+      </c>
+      <c r="O124" s="2"/>
+      <c r="P124" s="1">
+        <f t="shared" si="15"/>
+        <v>7</v>
+      </c>
+      <c r="Q124" s="4">
+        <v>46476</v>
+      </c>
+      <c r="R124" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="S124" s="2"/>
+      <c r="T124" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="U124" s="2">
+        <f t="shared" si="19"/>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="125" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A125" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B125" s="2"/>
+      <c r="C125" s="2"/>
+      <c r="D125" s="1">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="E125" s="2"/>
+      <c r="F125" s="1">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="G125" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="H125" s="1">
+        <f t="shared" si="22"/>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="I125" s="1">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="J125" s="1">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="K125" s="2"/>
+      <c r="L125" s="3">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="M125" s="2"/>
+      <c r="N125" s="2">
+        <v>30</v>
+      </c>
+      <c r="O125" s="2"/>
+      <c r="P125" s="1">
+        <f t="shared" si="15"/>
+        <v>7</v>
+      </c>
+      <c r="Q125" s="4">
+        <v>46507</v>
+      </c>
+      <c r="R125" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="S125" s="2"/>
+      <c r="T125" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="U125" s="2">
+        <f t="shared" si="19"/>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="126" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A126" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B126" s="2"/>
+      <c r="C126" s="2"/>
+      <c r="D126" s="1">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="E126" s="2"/>
+      <c r="F126" s="1">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="G126" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="H126" s="1">
+        <f t="shared" si="22"/>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="I126" s="1">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="J126" s="1">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="K126" s="2"/>
+      <c r="L126" s="3">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="M126" s="2"/>
+      <c r="N126" s="2">
+        <v>31</v>
+      </c>
+      <c r="O126" s="2"/>
+      <c r="P126" s="1">
+        <f t="shared" si="15"/>
+        <v>7</v>
+      </c>
+      <c r="Q126" s="4">
+        <v>46538</v>
+      </c>
+      <c r="R126" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="S126" s="2"/>
+      <c r="T126" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="U126" s="2">
+        <f t="shared" si="19"/>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="127" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A127" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B127" s="2"/>
+      <c r="C127" s="2"/>
+      <c r="D127" s="1">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="E127" s="2"/>
+      <c r="F127" s="1">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="G127" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="H127" s="1">
+        <f t="shared" si="22"/>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="I127" s="1">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="J127" s="1">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="K127" s="2"/>
+      <c r="L127" s="3">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="M127" s="2"/>
+      <c r="N127" s="2">
+        <v>30</v>
+      </c>
+      <c r="O127" s="2"/>
+      <c r="P127" s="1">
+        <f t="shared" si="15"/>
+        <v>7</v>
+      </c>
+      <c r="Q127" s="4">
+        <v>46568</v>
+      </c>
+      <c r="R127" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="S127" s="2"/>
+      <c r="T127" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="U127" s="2">
+        <f t="shared" si="19"/>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="128" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A128" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B128" s="2"/>
+      <c r="C128" s="2"/>
+      <c r="D128" s="1">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="E128" s="2"/>
+      <c r="F128" s="1">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="G128" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="H128" s="1">
+        <f t="shared" si="22"/>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="I128" s="1">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="J128" s="1">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="K128" s="2"/>
+      <c r="L128" s="3">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="M128" s="2"/>
+      <c r="N128" s="2">
+        <v>31</v>
+      </c>
+      <c r="O128" s="2"/>
+      <c r="P128" s="1">
+        <f t="shared" si="15"/>
+        <v>7</v>
+      </c>
+      <c r="Q128" s="4">
+        <v>46599</v>
+      </c>
+      <c r="R128" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="S128" s="2"/>
+      <c r="T128" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="U128" s="2">
+        <f t="shared" si="19"/>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="129" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A129" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B129" s="2"/>
+      <c r="C129" s="2"/>
+      <c r="D129" s="1">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="E129" s="2"/>
+      <c r="F129" s="1">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="G129" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="H129" s="1">
+        <f t="shared" si="22"/>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="I129" s="1">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="J129" s="1">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="K129" s="2"/>
+      <c r="L129" s="3">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="M129" s="2"/>
+      <c r="N129" s="2">
+        <v>31</v>
+      </c>
+      <c r="O129" s="2"/>
+      <c r="P129" s="1">
+        <f t="shared" si="15"/>
+        <v>7</v>
+      </c>
+      <c r="Q129" s="4">
+        <v>46630</v>
+      </c>
+      <c r="R129" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="S129" s="2"/>
+      <c r="T129" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="U129" s="2">
+        <f t="shared" si="19"/>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="130" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A130" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B130" s="2"/>
+      <c r="C130" s="2"/>
+      <c r="D130" s="1">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="E130" s="2"/>
+      <c r="F130" s="1">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="G130" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="H130" s="1">
+        <f t="shared" si="22"/>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="I130" s="1">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="J130" s="1">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="K130" s="2"/>
+      <c r="L130" s="3">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="M130" s="2"/>
+      <c r="N130" s="2">
+        <v>30</v>
+      </c>
+      <c r="O130" s="2"/>
+      <c r="P130" s="1">
+        <f t="shared" si="15"/>
+        <v>7</v>
+      </c>
+      <c r="Q130" s="4">
+        <v>46660</v>
+      </c>
+      <c r="R130" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="S130" s="2"/>
+      <c r="T130" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="U130" s="2">
+        <f t="shared" si="19"/>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="131" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A131" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B131" s="2"/>
+      <c r="C131" s="2"/>
+      <c r="D131" s="1">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="E131" s="2"/>
+      <c r="F131" s="1">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="G131" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="H131" s="1">
+        <f t="shared" si="22"/>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="I131" s="1">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="J131" s="1">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="K131" s="2"/>
+      <c r="L131" s="3">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="M131" s="2"/>
+      <c r="N131" s="2">
+        <v>31</v>
+      </c>
+      <c r="O131" s="2"/>
+      <c r="P131" s="1">
+        <f t="shared" si="15"/>
+        <v>7</v>
+      </c>
+      <c r="Q131" s="4">
+        <v>46691</v>
+      </c>
+      <c r="R131" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="S131" s="2"/>
+      <c r="T131" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="U131" s="2">
+        <f t="shared" si="19"/>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="132" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A132" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B132" s="2"/>
+      <c r="C132" s="2"/>
+      <c r="D132" s="1">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="E132" s="2"/>
+      <c r="F132" s="1">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="G132" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="H132" s="1">
+        <f t="shared" si="22"/>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="I132" s="1">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="J132" s="1">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="K132" s="2"/>
+      <c r="L132" s="3">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="M132" s="2"/>
+      <c r="N132" s="2">
+        <v>30</v>
+      </c>
+      <c r="O132" s="2"/>
+      <c r="P132" s="1">
+        <f t="shared" si="15"/>
+        <v>7</v>
+      </c>
+      <c r="Q132" s="4">
+        <v>46721</v>
+      </c>
+      <c r="R132" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="S132" s="2"/>
+      <c r="T132" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="U132" s="2">
+        <f t="shared" si="19"/>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="133" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A133" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="B133" s="11"/>
+      <c r="C133" s="11"/>
+      <c r="D133" s="13">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="E133" s="11"/>
+      <c r="F133" s="13">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="G133" s="11">
+        <v>1.5</v>
+      </c>
+      <c r="H133" s="13">
+        <f t="shared" si="22"/>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="I133" s="13">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="J133" s="13">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="K133" s="11"/>
+      <c r="L133" s="14">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="M133" s="11"/>
+      <c r="N133" s="11">
+        <v>31</v>
+      </c>
+      <c r="O133" s="11"/>
+      <c r="P133" s="13">
+        <f t="shared" si="15"/>
+        <v>7</v>
+      </c>
+      <c r="Q133" s="4">
+        <v>46752</v>
+      </c>
+      <c r="R133" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="S133" s="2"/>
+      <c r="T133" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="U133" s="2">
+        <f t="shared" si="19"/>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="134" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A134" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B134" s="2"/>
+      <c r="C134" s="2"/>
+      <c r="D134" s="13">
+        <f t="shared" ref="D134:D140" si="26">ROUND(B134*C134,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E134" s="11"/>
+      <c r="F134" s="13">
+        <f t="shared" ref="F134:F140" si="27">ROUND(B134*E134,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G134" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="H134" s="13">
+        <f t="shared" ref="H134:H140" si="28">G134/100</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="I134" s="13">
+        <f t="shared" ref="I134:I140" si="29">+C134*0.07</f>
+        <v>0</v>
+      </c>
+      <c r="J134" s="13">
+        <f t="shared" ref="J134:J140" si="30">ROUND(B134*I134,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K134" s="2"/>
+      <c r="L134" s="14">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="M134" s="2"/>
+      <c r="N134" s="2">
+        <v>31</v>
+      </c>
+      <c r="O134" s="2"/>
+      <c r="P134" s="13">
+        <f t="shared" si="15"/>
+        <v>7</v>
+      </c>
+      <c r="Q134" s="10" t="str">
+        <f>_xlfn.CONCAT(N134,"-",RIGHT(A134,2),"-",LEFT(A134,4))</f>
+        <v>31-01-2028</v>
+      </c>
+      <c r="R134" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="S134" s="2"/>
+      <c r="T134" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="U134" s="2">
+        <f t="shared" si="19"/>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="135" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A135" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B135" s="2"/>
+      <c r="C135" s="2"/>
+      <c r="D135" s="1">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="E135" s="2"/>
+      <c r="F135" s="1">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="G135" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="H135" s="1">
+        <f t="shared" si="28"/>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="I135" s="1">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="J135" s="1">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="K135" s="2"/>
+      <c r="L135" s="3">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="M135" s="2"/>
+      <c r="N135" s="2">
+        <v>30</v>
+      </c>
+      <c r="O135" s="2"/>
+      <c r="P135" s="1">
+        <f t="shared" si="15"/>
+        <v>7</v>
+      </c>
+      <c r="Q135" s="10" t="str">
+        <f t="shared" ref="Q135:Q140" si="31">_xlfn.CONCAT(N135,"-",RIGHT(A135,2),"-",LEFT(A135,4))</f>
+        <v>30-02-2028</v>
+      </c>
+      <c r="R135" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="S135" s="2"/>
+      <c r="T135" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="U135" s="2">
+        <f t="shared" si="19"/>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="136" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A136" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B136" s="2"/>
+      <c r="C136" s="2"/>
+      <c r="D136" s="1">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="E136" s="2"/>
+      <c r="F136" s="1">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="G136" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="H136" s="1">
+        <f t="shared" si="28"/>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="I136" s="1">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="J136" s="1">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="K136" s="2"/>
+      <c r="L136" s="3">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="M136" s="2"/>
+      <c r="N136" s="2">
+        <v>31</v>
+      </c>
+      <c r="O136" s="2"/>
+      <c r="P136" s="1">
+        <f t="shared" si="15"/>
+        <v>7</v>
+      </c>
+      <c r="Q136" s="10" t="str">
+        <f t="shared" si="31"/>
+        <v>31-03-2028</v>
+      </c>
+      <c r="R136" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="S136" s="2"/>
+      <c r="T136" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="U136" s="2">
+        <f t="shared" si="19"/>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="137" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A137" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B137" s="2"/>
+      <c r="C137" s="2"/>
+      <c r="D137" s="1">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="E137" s="2"/>
+      <c r="F137" s="1">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="G137" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="H137" s="1">
+        <f t="shared" si="28"/>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="I137" s="1">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="J137" s="1">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="K137" s="2"/>
+      <c r="L137" s="3">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="M137" s="2"/>
+      <c r="N137" s="2">
+        <v>30</v>
+      </c>
+      <c r="O137" s="2"/>
+      <c r="P137" s="1">
+        <f t="shared" si="15"/>
+        <v>7</v>
+      </c>
+      <c r="Q137" s="10" t="str">
+        <f t="shared" si="31"/>
+        <v>30-04-2028</v>
+      </c>
+      <c r="R137" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="S137" s="2"/>
+      <c r="T137" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="U137" s="2">
+        <f t="shared" si="19"/>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="138" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A138" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B138" s="2"/>
+      <c r="C138" s="2"/>
+      <c r="D138" s="1">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="E138" s="2"/>
+      <c r="F138" s="1">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="G138" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="H138" s="1">
+        <f t="shared" si="28"/>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="I138" s="1">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="J138" s="1">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="K138" s="2"/>
+      <c r="L138" s="3">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="M138" s="2"/>
+      <c r="N138" s="2">
+        <v>31</v>
+      </c>
+      <c r="O138" s="2"/>
+      <c r="P138" s="1">
+        <f t="shared" si="15"/>
+        <v>7</v>
+      </c>
+      <c r="Q138" s="10" t="str">
+        <f t="shared" si="31"/>
+        <v>31-05-2028</v>
+      </c>
+      <c r="R138" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="S138" s="2"/>
+      <c r="T138" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="U138" s="2">
+        <f t="shared" si="19"/>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="139" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A139" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B139" s="2"/>
+      <c r="C139" s="2"/>
+      <c r="D139" s="1">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="E139" s="2"/>
+      <c r="F139" s="1">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="G139" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="H139" s="1">
+        <f t="shared" si="28"/>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="I139" s="1">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="J139" s="1">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="K139" s="2"/>
+      <c r="L139" s="3">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="M139" s="2"/>
+      <c r="N139" s="2">
+        <v>30</v>
+      </c>
+      <c r="O139" s="2"/>
+      <c r="P139" s="1">
+        <f t="shared" ref="P139:P140" si="32">7-O139</f>
+        <v>7</v>
+      </c>
+      <c r="Q139" s="10" t="str">
+        <f t="shared" si="31"/>
+        <v>30-06-2028</v>
+      </c>
+      <c r="R139" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="S139" s="2"/>
+      <c r="T139" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="U139" s="2">
+        <f t="shared" si="19"/>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="140" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A140" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B140" s="2"/>
+      <c r="C140" s="2"/>
+      <c r="D140" s="1">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="E140" s="2"/>
+      <c r="F140" s="1">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="G140" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="H140" s="1">
+        <f t="shared" si="28"/>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="I140" s="1">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="J140" s="1">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="K140" s="2"/>
+      <c r="L140" s="3">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="M140" s="2"/>
+      <c r="N140" s="2">
+        <v>31</v>
+      </c>
+      <c r="O140" s="2"/>
+      <c r="P140" s="1">
+        <f t="shared" si="32"/>
+        <v>7</v>
+      </c>
+      <c r="Q140" s="10" t="str">
+        <f t="shared" si="31"/>
+        <v>31-07-2028</v>
+      </c>
+      <c r="R140" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="S140" s="2"/>
+      <c r="T140" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="U140" s="2">
+        <f t="shared" si="19"/>
+        <v>1.5</v>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF126C7F-EAC0-4D1A-AFBC-30614064DF09}">
-  <dimension ref="A1:J19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="60" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="B2" s="2">
-        <v>26318.21</v>
-      </c>
-      <c r="F2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="B3" s="2">
-        <v>75.7</v>
-      </c>
-      <c r="F3" t="s">
-        <v>133</v>
-      </c>
-      <c r="J3">
-        <v>252757</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="B4" s="1">
-        <f>ROUND(B2*B3,0)</f>
-        <v>1992288</v>
-      </c>
-      <c r="F4" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="B5" s="2">
-        <v>113.5</v>
-      </c>
-      <c r="F5" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="B6" s="1">
-        <f>ROUND(B2*B5,0)</f>
-        <v>2987117</v>
-      </c>
-      <c r="F6" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="B7" s="2">
-        <v>1.41</v>
-      </c>
-      <c r="F7" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="B8" s="1">
-        <f>B7/100</f>
-        <v>1.41E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="B9" s="1">
-        <f>+B3*0.07</f>
-        <v>5.2990000000000004</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="B10" s="1">
-        <f>ROUND(B2*B9,0)</f>
-        <v>139460</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="B11" s="2">
-        <v>264000</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="B12" s="3">
-        <f>ROUND((B11*4.75)/12,0)</f>
-        <v>104500</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="B13" s="2">
-        <v>46229</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="B14" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="B15" s="2"/>
-    </row>
-    <row r="16" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="B16" s="2"/>
-    </row>
-    <row r="17" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B17" s="4" t="str">
-        <f>_xlfn.CONCAT(B14,"/","01/2017")</f>
-        <v>31/01/2017</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B18" s="2"/>
-    </row>
-    <row r="19" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B19" s="4"/>
-    </row>
-  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>